--- a/Excels/DSR.xlsx
+++ b/Excels/DSR.xlsx
@@ -3125,6 +3125,2077 @@
         </is>
       </c>
     </row>
+    <row r="36" spans="1:31">
+      <c r="A36" s="0">
+        <v>196</v>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>Fantastic Holland</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI (3)</t>
+        </is>
+      </c>
+      <c r="K36" s="0">
+        <v>8300</v>
+      </c>
+      <c r="L36" s="0">
+        <v>1</v>
+      </c>
+      <c r="N36" s="0">
+        <v>8300</v>
+      </c>
+      <c r="O36" s="0">
+        <v>8300</v>
+      </c>
+      <c r="P36" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q36" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R36" s="0" t="inlineStr">
+        <is>
+          <t>S4398 Edit S4398Clone</t>
+        </is>
+      </c>
+      <c r="S36" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-04:59 pm</t>
+        </is>
+      </c>
+      <c r="T36" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U36" s="0">
+        <v>1</v>
+      </c>
+      <c r="V36" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W36" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Indoor And Outdoor Customers  </t>
+        </is>
+      </c>
+      <c r="Z36" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>8300</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>8300</v>
+      </c>
+      <c r="AC36" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦9,000.00Cash: -₦700.00</t>
+        </is>
+      </c>
+      <c r="AD36" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:31">
+      <c r="A37" s="0">
+        <v>197</v>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>Lagos laffaya lace B</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>LAFAYYA</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR (2)</t>
+        </is>
+      </c>
+      <c r="K37" s="0">
+        <v>20000</v>
+      </c>
+      <c r="L37" s="0">
+        <v>2</v>
+      </c>
+      <c r="N37" s="0">
+        <v>40000</v>
+      </c>
+      <c r="O37" s="0">
+        <v>40000</v>
+      </c>
+      <c r="P37" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q37" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R37" s="0" t="inlineStr">
+        <is>
+          <t>S4399 Edit S4399Clone</t>
+        </is>
+      </c>
+      <c r="S37" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-04:59 pm</t>
+        </is>
+      </c>
+      <c r="T37" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U37" s="0">
+        <v>2</v>
+      </c>
+      <c r="V37" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W37" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Indoor And Outdoor Customers  </t>
+        </is>
+      </c>
+      <c r="Z37" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>40000</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>40000</v>
+      </c>
+      <c r="AC37" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦40,000.00</t>
+        </is>
+      </c>
+      <c r="AD37" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:31">
+      <c r="A38" s="0">
+        <v>117</v>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>EMBELLISHED MDT</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K38" s="0">
+        <v>17500</v>
+      </c>
+      <c r="L38" s="0">
+        <v>4</v>
+      </c>
+      <c r="N38" s="0">
+        <v>70000</v>
+      </c>
+      <c r="O38" s="0">
+        <v>70000</v>
+      </c>
+      <c r="P38" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q38" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R38" s="0" t="inlineStr">
+        <is>
+          <t>S4400 Edit S4400Clone</t>
+        </is>
+      </c>
+      <c r="S38" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:02 pm</t>
+        </is>
+      </c>
+      <c r="T38" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U38" s="0">
+        <v>8</v>
+      </c>
+      <c r="V38" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W38" s="0" t="inlineStr">
+        <is>
+          <t>Shamsu Shop </t>
+        </is>
+      </c>
+      <c r="Z38" s="0">
+        <v>27</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>166000</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>166000</v>
+      </c>
+      <c r="AC38" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦169,000.00Cash: -₦3,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:31">
+      <c r="A39" s="0">
+        <v>150</v>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>LAGOS LACE C</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>LACE</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K39" s="0">
+        <v>24000</v>
+      </c>
+      <c r="L39" s="0">
+        <v>4</v>
+      </c>
+      <c r="N39" s="0">
+        <v>96000</v>
+      </c>
+      <c r="O39" s="0">
+        <v>96000</v>
+      </c>
+      <c r="P39" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q39" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R39" s="0" t="inlineStr">
+        <is>
+          <t>S4400 Edit S4400Clone</t>
+        </is>
+      </c>
+      <c r="S39" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:02 pm</t>
+        </is>
+      </c>
+      <c r="T39" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U39" s="0">
+        <v>8</v>
+      </c>
+      <c r="V39" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W39" s="0" t="inlineStr">
+        <is>
+          <t>Shamsu Shop </t>
+        </is>
+      </c>
+      <c r="Z39" s="0">
+        <v>27</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>166000</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>166000</v>
+      </c>
+      <c r="AC39" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦169,000.00Cash: -₦3,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
+      <c r="A40" s="0">
+        <v>126</v>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>HOLLAND MEDIUM</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K40" s="0">
+        <v>12000</v>
+      </c>
+      <c r="L40" s="0">
+        <v>3</v>
+      </c>
+      <c r="N40" s="0">
+        <v>36000</v>
+      </c>
+      <c r="O40" s="0">
+        <v>36000</v>
+      </c>
+      <c r="P40" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q40" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R40" s="0" t="inlineStr">
+        <is>
+          <t>S4401 Edit S4401Clone</t>
+        </is>
+      </c>
+      <c r="S40" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:03 pm</t>
+        </is>
+      </c>
+      <c r="T40" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U40" s="0">
+        <v>3</v>
+      </c>
+      <c r="V40" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W40" s="0" t="inlineStr">
+        <is>
+          <t>MAIMUNA HASSAN</t>
+        </is>
+      </c>
+      <c r="Z40" s="0">
+        <v>323</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>36000</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>36000</v>
+      </c>
+      <c r="AC40" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦36,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:31">
+      <c r="A41" s="0">
+        <v>134</v>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>HIGHTEST</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K41" s="0">
+        <v>10500</v>
+      </c>
+      <c r="L41" s="0">
+        <v>4</v>
+      </c>
+      <c r="N41" s="0">
+        <v>42000</v>
+      </c>
+      <c r="O41" s="0">
+        <v>42000</v>
+      </c>
+      <c r="P41" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q41" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R41" s="0" t="inlineStr">
+        <is>
+          <t>S4402 Edit S4402Clone</t>
+        </is>
+      </c>
+      <c r="S41" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:03 pm</t>
+        </is>
+      </c>
+      <c r="T41" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U41" s="0">
+        <v>4</v>
+      </c>
+      <c r="V41" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W41" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z41" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>42000</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>42000</v>
+      </c>
+      <c r="AC41" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦42,000.00</t>
+        </is>
+      </c>
+      <c r="AD41" s="0" t="inlineStr">
+        <is>
+          <t>ALH NASIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:31">
+      <c r="A42" s="0">
+        <v>139</v>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY INDIA</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K42" s="0">
+        <v>7700</v>
+      </c>
+      <c r="L42" s="0">
+        <v>5</v>
+      </c>
+      <c r="N42" s="0">
+        <v>38500</v>
+      </c>
+      <c r="O42" s="0">
+        <v>38500</v>
+      </c>
+      <c r="P42" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q42" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R42" s="0" t="inlineStr">
+        <is>
+          <t>S4403 Edit S4403Clone</t>
+        </is>
+      </c>
+      <c r="S42" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:04 pm</t>
+        </is>
+      </c>
+      <c r="T42" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U42" s="0">
+        <v>20</v>
+      </c>
+      <c r="V42" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W42" s="0" t="inlineStr">
+        <is>
+          <t>HAJ SUMAYYA </t>
+        </is>
+      </c>
+      <c r="Z42" s="0">
+        <v>324</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>110500</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>110500</v>
+      </c>
+      <c r="AC42" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦110,500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:31">
+      <c r="A43" s="0">
+        <v>141</v>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>BELLDAM</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K43" s="0">
+        <v>4800</v>
+      </c>
+      <c r="L43" s="0">
+        <v>15</v>
+      </c>
+      <c r="N43" s="0">
+        <v>72000</v>
+      </c>
+      <c r="O43" s="0">
+        <v>72000</v>
+      </c>
+      <c r="P43" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q43" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R43" s="0" t="inlineStr">
+        <is>
+          <t>S4403 Edit S4403Clone</t>
+        </is>
+      </c>
+      <c r="S43" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:04 pm</t>
+        </is>
+      </c>
+      <c r="T43" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U43" s="0">
+        <v>20</v>
+      </c>
+      <c r="V43" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W43" s="0" t="inlineStr">
+        <is>
+          <t>HAJ SUMAYYA </t>
+        </is>
+      </c>
+      <c r="Z43" s="0">
+        <v>324</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>110500</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>110500</v>
+      </c>
+      <c r="AC43" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦110,500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:31">
+      <c r="A44" s="0">
+        <v>85</v>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>ELIZABETH EMBELLISHED</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K44" s="0">
+        <v>38000</v>
+      </c>
+      <c r="L44" s="0">
+        <v>1</v>
+      </c>
+      <c r="N44" s="0">
+        <v>38000</v>
+      </c>
+      <c r="O44" s="0">
+        <v>38000</v>
+      </c>
+      <c r="P44" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q44" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R44" s="0" t="inlineStr">
+        <is>
+          <t>S4404 Edit S4404Clone</t>
+        </is>
+      </c>
+      <c r="S44" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:36 pm</t>
+        </is>
+      </c>
+      <c r="T44" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U44" s="0">
+        <v>1</v>
+      </c>
+      <c r="V44" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W44" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z44" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>38000</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>38000</v>
+      </c>
+      <c r="AC44" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦38,000.00</t>
+        </is>
+      </c>
+      <c r="AD44" s="0" t="inlineStr">
+        <is>
+          <t>KABUWAYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:31">
+      <c r="A45" s="0">
+        <v>150</v>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>LAGOS LACE C</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>LACE</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K45" s="0">
+        <v>25000</v>
+      </c>
+      <c r="L45" s="0">
+        <v>1</v>
+      </c>
+      <c r="N45" s="0">
+        <v>25000</v>
+      </c>
+      <c r="O45" s="0">
+        <v>25000</v>
+      </c>
+      <c r="P45" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q45" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R45" s="0" t="inlineStr">
+        <is>
+          <t>S4405 Edit S4405Clone</t>
+        </is>
+      </c>
+      <c r="S45" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:37 pm</t>
+        </is>
+      </c>
+      <c r="T45" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U45" s="0">
+        <v>1</v>
+      </c>
+      <c r="V45" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W45" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Indoor And Outdoor Customers  </t>
+        </is>
+      </c>
+      <c r="Z45" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>25000</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>25000</v>
+      </c>
+      <c r="AC45" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦25,000.00</t>
+        </is>
+      </c>
+      <c r="AD45" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:31">
+      <c r="A46" s="0">
+        <v>126</v>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>HOLLAND MEDIUM</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K46" s="0">
+        <v>11800</v>
+      </c>
+      <c r="L46" s="0">
+        <v>4</v>
+      </c>
+      <c r="N46" s="0">
+        <v>47200</v>
+      </c>
+      <c r="O46" s="0">
+        <v>47200</v>
+      </c>
+      <c r="P46" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q46" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R46" s="0" t="inlineStr">
+        <is>
+          <t>S4406 Edit S4406Clone</t>
+        </is>
+      </c>
+      <c r="S46" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:37 pm</t>
+        </is>
+      </c>
+      <c r="T46" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U46" s="0">
+        <v>4</v>
+      </c>
+      <c r="V46" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W46" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Indoor And Outdoor Customers  </t>
+        </is>
+      </c>
+      <c r="Z46" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>47200</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>47200</v>
+      </c>
+      <c r="AC46" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦47,200.00</t>
+        </is>
+      </c>
+      <c r="AD46" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:31">
+      <c r="A47" s="0">
+        <v>142</v>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>HIGHOLLAND</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K47" s="0">
+        <v>4400</v>
+      </c>
+      <c r="L47" s="0">
+        <v>24</v>
+      </c>
+      <c r="N47" s="0">
+        <v>105600</v>
+      </c>
+      <c r="O47" s="0">
+        <v>105600</v>
+      </c>
+      <c r="P47" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q47" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R47" s="0" t="inlineStr">
+        <is>
+          <t>S4407 Edit S4407Clone</t>
+        </is>
+      </c>
+      <c r="S47" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:38 pm</t>
+        </is>
+      </c>
+      <c r="T47" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U47" s="0">
+        <v>24</v>
+      </c>
+      <c r="V47" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W47" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z47" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>105500</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>105500</v>
+      </c>
+      <c r="AC47" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦105,500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:31">
+      <c r="A48" s="0">
+        <v>195</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K48" s="0">
+        <v>100</v>
+      </c>
+      <c r="L48" s="0">
+        <v>-1</v>
+      </c>
+      <c r="N48" s="0">
+        <v>-100</v>
+      </c>
+      <c r="O48" s="0">
+        <v>-100</v>
+      </c>
+      <c r="P48" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q48" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R48" s="0" t="inlineStr">
+        <is>
+          <t>S4407 Edit S4407Clone</t>
+        </is>
+      </c>
+      <c r="S48" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:38 pm</t>
+        </is>
+      </c>
+      <c r="T48" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U48" s="0">
+        <v>24</v>
+      </c>
+      <c r="V48" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W48" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z48" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>105500</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>105500</v>
+      </c>
+      <c r="AC48" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦105,500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:31">
+      <c r="A49" s="0">
+        <v>141</v>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>BELLDAM</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K49" s="0">
+        <v>5000</v>
+      </c>
+      <c r="L49" s="0">
+        <v>2</v>
+      </c>
+      <c r="N49" s="0">
+        <v>10000</v>
+      </c>
+      <c r="O49" s="0">
+        <v>10000</v>
+      </c>
+      <c r="P49" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q49" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R49" s="0" t="inlineStr">
+        <is>
+          <t>S4408 Edit S4408Clone</t>
+        </is>
+      </c>
+      <c r="S49" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:43 pm</t>
+        </is>
+      </c>
+      <c r="T49" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U49" s="0">
+        <v>2</v>
+      </c>
+      <c r="V49" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W49" s="0" t="inlineStr">
+        <is>
+          <t>Fahad Tahir </t>
+        </is>
+      </c>
+      <c r="Z49" s="0">
+        <v>22</v>
+      </c>
+      <c r="AA49" s="0">
+        <v>10000</v>
+      </c>
+      <c r="AB49" s="0">
+        <v>10000</v>
+      </c>
+      <c r="AC49" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦10,000.00</t>
+        </is>
+      </c>
+      <c r="AD49" s="0" t="inlineStr">
+        <is>
+          <t>MAMAN AHMAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:31">
+      <c r="A50" s="0">
+        <v>90</v>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>ABS SUPER EMBELLISHED </t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K50" s="0">
+        <v>30000</v>
+      </c>
+      <c r="L50" s="0">
+        <v>6</v>
+      </c>
+      <c r="N50" s="0">
+        <v>180000</v>
+      </c>
+      <c r="O50" s="0">
+        <v>180000</v>
+      </c>
+      <c r="P50" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q50" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R50" s="0" t="inlineStr">
+        <is>
+          <t>S4409 Edit S4409Clone</t>
+        </is>
+      </c>
+      <c r="S50" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:44 pm</t>
+        </is>
+      </c>
+      <c r="T50" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U50" s="0">
+        <v>6</v>
+      </c>
+      <c r="V50" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W50" s="0" t="inlineStr">
+        <is>
+          <t>ZAHRA LATEST </t>
+        </is>
+      </c>
+      <c r="Z50" s="0">
+        <v>325</v>
+      </c>
+      <c r="AA50" s="0">
+        <v>180000</v>
+      </c>
+      <c r="AB50" s="0">
+        <v>180000</v>
+      </c>
+      <c r="AC50" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦180,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:31">
+      <c r="A51" s="0">
+        <v>139</v>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY INDIA</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K51" s="0">
+        <v>8000</v>
+      </c>
+      <c r="L51" s="0">
+        <v>2</v>
+      </c>
+      <c r="N51" s="0">
+        <v>16000</v>
+      </c>
+      <c r="O51" s="0">
+        <v>16000</v>
+      </c>
+      <c r="P51" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q51" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R51" s="0" t="inlineStr">
+        <is>
+          <t>S4410 Edit S4410Clone</t>
+        </is>
+      </c>
+      <c r="S51" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:44 pm</t>
+        </is>
+      </c>
+      <c r="T51" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U51" s="0">
+        <v>2</v>
+      </c>
+      <c r="V51" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W51" s="0" t="inlineStr">
+        <is>
+          <t>Fahad Tahir </t>
+        </is>
+      </c>
+      <c r="Z51" s="0">
+        <v>22</v>
+      </c>
+      <c r="AA51" s="0">
+        <v>16000</v>
+      </c>
+      <c r="AB51" s="0">
+        <v>16000</v>
+      </c>
+      <c r="AC51" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦16,000.00</t>
+        </is>
+      </c>
+      <c r="AD51" s="0" t="inlineStr">
+        <is>
+          <t>MAMAN FARHAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:31">
+      <c r="A52" s="0">
+        <v>78</v>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>JULIUS CRYSTAL SHINE</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K52" s="0">
+        <v>95000</v>
+      </c>
+      <c r="L52" s="0">
+        <v>1</v>
+      </c>
+      <c r="N52" s="0">
+        <v>95000</v>
+      </c>
+      <c r="O52" s="0">
+        <v>95000</v>
+      </c>
+      <c r="P52" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q52" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R52" s="0" t="inlineStr">
+        <is>
+          <t>S4411 Edit S4411Clone</t>
+        </is>
+      </c>
+      <c r="S52" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:45 pm</t>
+        </is>
+      </c>
+      <c r="T52" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U52" s="0">
+        <v>5</v>
+      </c>
+      <c r="V52" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W52" s="0" t="inlineStr">
+        <is>
+          <t>NURHAF </t>
+        </is>
+      </c>
+      <c r="Z52" s="0">
+        <v>33</v>
+      </c>
+      <c r="AA52" s="0">
+        <v>156400</v>
+      </c>
+      <c r="AB52" s="0">
+        <v>156400</v>
+      </c>
+      <c r="AC52" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦156,400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:31">
+      <c r="A53" s="0">
+        <v>86</v>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>LATEST ULTRA EMBELLISHED </t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K53" s="0">
+        <v>38000</v>
+      </c>
+      <c r="L53" s="0">
+        <v>1</v>
+      </c>
+      <c r="N53" s="0">
+        <v>38000</v>
+      </c>
+      <c r="O53" s="0">
+        <v>38000</v>
+      </c>
+      <c r="P53" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q53" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R53" s="0" t="inlineStr">
+        <is>
+          <t>S4411 Edit S4411Clone</t>
+        </is>
+      </c>
+      <c r="S53" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:45 pm</t>
+        </is>
+      </c>
+      <c r="T53" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U53" s="0">
+        <v>5</v>
+      </c>
+      <c r="V53" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W53" s="0" t="inlineStr">
+        <is>
+          <t>NURHAF </t>
+        </is>
+      </c>
+      <c r="Z53" s="0">
+        <v>33</v>
+      </c>
+      <c r="AA53" s="0">
+        <v>156400</v>
+      </c>
+      <c r="AB53" s="0">
+        <v>156400</v>
+      </c>
+      <c r="AC53" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦156,400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="1:31">
+      <c r="A54" s="0">
+        <v>139</v>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY INDIA</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K54" s="0">
+        <v>7800</v>
+      </c>
+      <c r="L54" s="0">
+        <v>3</v>
+      </c>
+      <c r="N54" s="0">
+        <v>23400</v>
+      </c>
+      <c r="O54" s="0">
+        <v>23400</v>
+      </c>
+      <c r="P54" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q54" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R54" s="0" t="inlineStr">
+        <is>
+          <t>S4411 Edit S4411Clone</t>
+        </is>
+      </c>
+      <c r="S54" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:45 pm</t>
+        </is>
+      </c>
+      <c r="T54" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U54" s="0">
+        <v>5</v>
+      </c>
+      <c r="V54" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W54" s="0" t="inlineStr">
+        <is>
+          <t>NURHAF </t>
+        </is>
+      </c>
+      <c r="Z54" s="0">
+        <v>33</v>
+      </c>
+      <c r="AA54" s="0">
+        <v>156400</v>
+      </c>
+      <c r="AB54" s="0">
+        <v>156400</v>
+      </c>
+      <c r="AC54" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦156,400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:31">
+      <c r="A55" s="0">
+        <v>78</v>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>JULIUS CRYSTAL SHINE</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K55" s="0">
+        <v>95000</v>
+      </c>
+      <c r="L55" s="0">
+        <v>3</v>
+      </c>
+      <c r="N55" s="0">
+        <v>285000</v>
+      </c>
+      <c r="O55" s="0">
+        <v>285000</v>
+      </c>
+      <c r="P55" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q55" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R55" s="0" t="inlineStr">
+        <is>
+          <t>S4412 Edit S4412Clone</t>
+        </is>
+      </c>
+      <c r="S55" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:46 pm</t>
+        </is>
+      </c>
+      <c r="T55" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U55" s="0">
+        <v>18</v>
+      </c>
+      <c r="V55" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W55" s="0" t="inlineStr">
+        <is>
+          <t>AMINA BAWA ROAD</t>
+        </is>
+      </c>
+      <c r="Z55" s="0">
+        <v>113</v>
+      </c>
+      <c r="AA55" s="0">
+        <v>405000</v>
+      </c>
+      <c r="AB55" s="0">
+        <v>405000</v>
+      </c>
+      <c r="AC55" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦405,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:31">
+      <c r="A56" s="0">
+        <v>139</v>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY INDIA</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K56" s="0">
+        <v>8000</v>
+      </c>
+      <c r="L56" s="0">
+        <v>15</v>
+      </c>
+      <c r="N56" s="0">
+        <v>120000</v>
+      </c>
+      <c r="O56" s="0">
+        <v>120000</v>
+      </c>
+      <c r="P56" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q56" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R56" s="0" t="inlineStr">
+        <is>
+          <t>S4412 Edit S4412Clone</t>
+        </is>
+      </c>
+      <c r="S56" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:46 pm</t>
+        </is>
+      </c>
+      <c r="T56" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U56" s="0">
+        <v>18</v>
+      </c>
+      <c r="V56" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W56" s="0" t="inlineStr">
+        <is>
+          <t>AMINA BAWA ROAD</t>
+        </is>
+      </c>
+      <c r="Z56" s="0">
+        <v>113</v>
+      </c>
+      <c r="AA56" s="0">
+        <v>405000</v>
+      </c>
+      <c r="AB56" s="0">
+        <v>405000</v>
+      </c>
+      <c r="AC56" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦405,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:31">
+      <c r="A57" s="0">
+        <v>138</v>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>HOLLANDAD</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K57" s="0">
+        <v>8500</v>
+      </c>
+      <c r="L57" s="0">
+        <v>20</v>
+      </c>
+      <c r="N57" s="0">
+        <v>170000</v>
+      </c>
+      <c r="O57" s="0">
+        <v>170000</v>
+      </c>
+      <c r="P57" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q57" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R57" s="0" t="inlineStr">
+        <is>
+          <t>S4413 Edit S4413Clone</t>
+        </is>
+      </c>
+      <c r="S57" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-05:47 pm</t>
+        </is>
+      </c>
+      <c r="T57" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U57" s="0">
+        <v>20</v>
+      </c>
+      <c r="V57" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W57" s="0" t="inlineStr">
+        <is>
+          <t>Fahad Tahir </t>
+        </is>
+      </c>
+      <c r="Z57" s="0">
+        <v>22</v>
+      </c>
+      <c r="AA57" s="0">
+        <v>170000</v>
+      </c>
+      <c r="AB57" s="0">
+        <v>170000</v>
+      </c>
+      <c r="AC57" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦170,000.00</t>
+        </is>
+      </c>
+      <c r="AD57" s="0" t="inlineStr">
+        <is>
+          <t>HAJ BINTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:31">
+      <c r="A58" s="0">
+        <v>104</v>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY COTTON POPLIN</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K58" s="0">
+        <v>26500</v>
+      </c>
+      <c r="L58" s="0">
+        <v>1</v>
+      </c>
+      <c r="N58" s="0">
+        <v>26500</v>
+      </c>
+      <c r="O58" s="0">
+        <v>26500</v>
+      </c>
+      <c r="P58" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q58" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R58" s="0" t="inlineStr">
+        <is>
+          <t>S4414 Edit S4414Clone</t>
+        </is>
+      </c>
+      <c r="S58" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-06:02 pm</t>
+        </is>
+      </c>
+      <c r="T58" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U58" s="0">
+        <v>1</v>
+      </c>
+      <c r="V58" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W58" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Indoor And Outdoor Customers  </t>
+        </is>
+      </c>
+      <c r="Z58" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA58" s="0">
+        <v>26500</v>
+      </c>
+      <c r="AB58" s="0">
+        <v>26500</v>
+      </c>
+      <c r="AC58" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦26,500.00</t>
+        </is>
+      </c>
+      <c r="AD58" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:31">
+      <c r="A59" s="0">
+        <v>106</v>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY COTONOU PLAIN</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K59" s="0">
+        <v>19000</v>
+      </c>
+      <c r="L59" s="0">
+        <v>4</v>
+      </c>
+      <c r="N59" s="0">
+        <v>76000</v>
+      </c>
+      <c r="O59" s="0">
+        <v>76000</v>
+      </c>
+      <c r="P59" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q59" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R59" s="0" t="inlineStr">
+        <is>
+          <t>S4415 Edit S4415Clone</t>
+        </is>
+      </c>
+      <c r="S59" s="0" t="inlineStr">
+        <is>
+          <t>08/03/2026-06:25 pm</t>
+        </is>
+      </c>
+      <c r="T59" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U59" s="0">
+        <v>4</v>
+      </c>
+      <c r="V59" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W59" s="0" t="inlineStr">
+        <is>
+          <t>Muhd Dan kasuwa Shop </t>
+        </is>
+      </c>
+      <c r="Z59" s="0">
+        <v>28</v>
+      </c>
+      <c r="AA59" s="0">
+        <v>76000</v>
+      </c>
+      <c r="AB59" s="0">
+        <v>76000</v>
+      </c>
+      <c r="AC59" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦76,000.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Excels/DSR.xlsx
+++ b/Excels/DSR.xlsx
@@ -211,21 +211,16 @@
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="0">
-        <v>194</v>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>Store Account Payment</t>
-        </is>
+        <v>86</v>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>Store Account Payment</t>
+          <t>LATEST ULTRA EMBELLISHED </t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>Store Account Payment</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
@@ -234,16 +229,16 @@
         </is>
       </c>
       <c r="K2" s="0">
-        <v>59900</v>
+        <v>39000</v>
       </c>
       <c r="L2" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N2" s="0">
-        <v>59900</v>
+        <v>156000</v>
       </c>
       <c r="O2" s="0">
-        <v>59900</v>
+        <v>156000</v>
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
@@ -257,12 +252,12 @@
       </c>
       <c r="R2" s="0" t="inlineStr">
         <is>
-          <t>P24 Edit P24Clone</t>
+          <t>S5577 Edit S5577Clone</t>
         </is>
       </c>
       <c r="S2" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-01:04 pm</t>
+          <t>09/07/2026-01:05 pm</t>
         </is>
       </c>
       <c r="T2" s="0" t="inlineStr">
@@ -270,48 +265,51 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="U2" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="U2" s="0">
+        <v>4</v>
       </c>
       <c r="V2" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W2" s="0" t="inlineStr">
         <is>
-          <t>MUKHTAR TAHIR </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z2" s="0">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AA2" s="0">
-        <v>59900</v>
+        <v>156000</v>
       </c>
       <c r="AB2" s="0">
-        <v>59900</v>
+        <v>156000</v>
       </c>
       <c r="AC2" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦59,900.00</t>
+          <t>MONIEPOINT: ₦156,000.00</t>
+        </is>
+      </c>
+      <c r="AD2" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:31">
       <c r="A3" s="0">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>HOLLAND WAX COLLECTION</t>
+          <t>HILTON JACQUARD VOILE </t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
@@ -320,16 +318,16 @@
         </is>
       </c>
       <c r="K3" s="0">
-        <v>140000</v>
+        <v>180000</v>
       </c>
       <c r="L3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="0">
-        <v>140000</v>
+        <v>360000</v>
       </c>
       <c r="O3" s="0">
-        <v>140000</v>
+        <v>360000</v>
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
@@ -343,12 +341,12 @@
       </c>
       <c r="R3" s="0" t="inlineStr">
         <is>
-          <t>S5139 Edit S5139Clone</t>
+          <t>S5578 Edit S5578Clone</t>
         </is>
       </c>
       <c r="S3" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:15 pm</t>
+          <t>09/07/2026-01:08 pm</t>
         </is>
       </c>
       <c r="T3" s="0" t="inlineStr">
@@ -357,7 +355,7 @@
         </is>
       </c>
       <c r="U3" s="0">
-        <v>1</v>
+        <v>-20</v>
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
@@ -366,36 +364,41 @@
       </c>
       <c r="W3" s="0" t="inlineStr">
         <is>
-          <t>SALIHU YABATEX</t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z3" s="0">
-        <v>258</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="0">
-        <v>140000</v>
+        <v>274000</v>
       </c>
       <c r="AB3" s="0">
-        <v>140000</v>
+        <v>274000</v>
       </c>
       <c r="AC3" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦140,000.00</t>
+          <t>MONIEPOINT: ₦274,000.00</t>
+        </is>
+      </c>
+      <c r="AD3" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:31">
       <c r="A4" s="0">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>SWISS LUXURY VOILE</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
@@ -404,16 +407,16 @@
         </is>
       </c>
       <c r="K4" s="0">
-        <v>20000</v>
+        <v>63000</v>
       </c>
       <c r="L4" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" s="0">
-        <v>20000</v>
+        <v>189000</v>
       </c>
       <c r="O4" s="0">
-        <v>20000</v>
+        <v>189000</v>
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
@@ -427,12 +430,12 @@
       </c>
       <c r="R4" s="0" t="inlineStr">
         <is>
-          <t>S5140 Edit S5140Clone</t>
+          <t>S5578 Edit S5578Clone</t>
         </is>
       </c>
       <c r="S4" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:16 pm</t>
+          <t>09/07/2026-01:08 pm</t>
         </is>
       </c>
       <c r="T4" s="0" t="inlineStr">
@@ -441,7 +444,7 @@
         </is>
       </c>
       <c r="U4" s="0">
-        <v>1</v>
+        <v>-20</v>
       </c>
       <c r="V4" s="0" t="inlineStr">
         <is>
@@ -450,36 +453,36 @@
       </c>
       <c r="W4" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z4" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA4" s="0">
-        <v>20000</v>
+        <v>274000</v>
       </c>
       <c r="AB4" s="0">
-        <v>20000</v>
+        <v>274000</v>
       </c>
       <c r="AC4" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦20,000.00</t>
+          <t>MONIEPOINT: ₦274,000.00</t>
         </is>
       </c>
       <c r="AD4" s="0" t="inlineStr">
         <is>
-          <t>MAMAN KHAIRAT</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="0">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>BRITISH HOLLAND PLAIN</t>
+          <t>HIGHTEST</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -493,16 +496,16 @@
         </is>
       </c>
       <c r="K5" s="0">
-        <v>30000</v>
+        <v>11000</v>
       </c>
       <c r="L5" s="0">
-        <v>1</v>
+        <v>-25</v>
       </c>
       <c r="N5" s="0">
-        <v>30000</v>
+        <v>-275000</v>
       </c>
       <c r="O5" s="0">
-        <v>30000</v>
+        <v>-275000</v>
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
@@ -516,12 +519,12 @@
       </c>
       <c r="R5" s="0" t="inlineStr">
         <is>
-          <t>S5141 Edit S5141Clone</t>
+          <t>S5578 Edit S5578Clone</t>
         </is>
       </c>
       <c r="S5" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:17 pm</t>
+          <t>09/07/2026-01:08 pm</t>
         </is>
       </c>
       <c r="T5" s="0" t="inlineStr">
@@ -530,7 +533,7 @@
         </is>
       </c>
       <c r="U5" s="0">
-        <v>11</v>
+        <v>-20</v>
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
@@ -539,31 +542,36 @@
       </c>
       <c r="W5" s="0" t="inlineStr">
         <is>
-          <t>HAJ LADIDI </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z5" s="0">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="AA5" s="0">
-        <v>250000</v>
+        <v>274000</v>
       </c>
       <c r="AB5" s="0">
-        <v>250000</v>
+        <v>274000</v>
       </c>
       <c r="AC5" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦250,000.00</t>
+          <t>MONIEPOINT: ₦274,000.00</t>
+        </is>
+      </c>
+      <c r="AD5" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:31">
       <c r="A6" s="0">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>IMPERIAL GRAND SATIN</t>
+          <t>CHIGANVY INDIA</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -577,16 +585,16 @@
         </is>
       </c>
       <c r="K6" s="0">
-        <v>30000</v>
+        <v>7700</v>
       </c>
       <c r="L6" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N6" s="0">
-        <v>60000</v>
+        <v>30800</v>
       </c>
       <c r="O6" s="0">
-        <v>60000</v>
+        <v>30800</v>
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
@@ -600,12 +608,12 @@
       </c>
       <c r="R6" s="0" t="inlineStr">
         <is>
-          <t>S5141 Edit S5141Clone</t>
+          <t>S5579 Edit S5579Clone</t>
         </is>
       </c>
       <c r="S6" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:17 pm</t>
+          <t>09/07/2026-01:31 pm</t>
         </is>
       </c>
       <c r="T6" s="0" t="inlineStr">
@@ -614,7 +622,7 @@
         </is>
       </c>
       <c r="U6" s="0">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V6" s="0" t="inlineStr">
         <is>
@@ -623,31 +631,36 @@
       </c>
       <c r="W6" s="0" t="inlineStr">
         <is>
-          <t>HAJ LADIDI </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z6" s="0">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="AA6" s="0">
-        <v>250000</v>
+        <v>30800</v>
       </c>
       <c r="AB6" s="0">
-        <v>250000</v>
+        <v>30800</v>
       </c>
       <c r="AC6" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦250,000.00</t>
+          <t>MONIEPOINT: ₦30,800.00</t>
+        </is>
+      </c>
+      <c r="AD6" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:31">
       <c r="A7" s="0">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>EMBELLISHED MDT</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -661,16 +674,16 @@
         </is>
       </c>
       <c r="K7" s="0">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="L7" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N7" s="0">
-        <v>160000</v>
+        <v>18000</v>
       </c>
       <c r="O7" s="0">
-        <v>160000</v>
+        <v>18000</v>
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
@@ -684,12 +697,12 @@
       </c>
       <c r="R7" s="0" t="inlineStr">
         <is>
-          <t>S5141 Edit S5141Clone</t>
+          <t>S5580 Edit S5580Clone</t>
         </is>
       </c>
       <c r="S7" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:17 pm</t>
+          <t>09/07/2026-01:32 pm</t>
         </is>
       </c>
       <c r="T7" s="0" t="inlineStr">
@@ -698,7 +711,7 @@
         </is>
       </c>
       <c r="U7" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="V7" s="0" t="inlineStr">
         <is>
@@ -707,31 +720,36 @@
       </c>
       <c r="W7" s="0" t="inlineStr">
         <is>
-          <t>HAJ LADIDI </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z7" s="0">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="AA7" s="0">
-        <v>250000</v>
+        <v>18000</v>
       </c>
       <c r="AB7" s="0">
-        <v>250000</v>
+        <v>18000</v>
       </c>
       <c r="AC7" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦250,000.00</t>
+          <t>MONIEPOINT: ₦18,000.00</t>
+        </is>
+      </c>
+      <c r="AD7" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="0">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>ROBA ATAMPA</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -745,16 +763,16 @@
         </is>
       </c>
       <c r="K8" s="0">
-        <v>15500</v>
+        <v>3000</v>
       </c>
       <c r="L8" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N8" s="0">
-        <v>93000</v>
+        <v>3000</v>
       </c>
       <c r="O8" s="0">
-        <v>93000</v>
+        <v>3000</v>
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
@@ -768,12 +786,12 @@
       </c>
       <c r="R8" s="0" t="inlineStr">
         <is>
-          <t>S5142 Edit S5142Clone</t>
+          <t>S5581 Edit S5581Clone</t>
         </is>
       </c>
       <c r="S8" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:18 pm</t>
+          <t>09/07/2026-01:32 pm</t>
         </is>
       </c>
       <c r="T8" s="0" t="inlineStr">
@@ -782,7 +800,7 @@
         </is>
       </c>
       <c r="U8" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V8" s="0" t="inlineStr">
         <is>
@@ -791,36 +809,36 @@
       </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z8" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA8" s="0">
-        <v>93000</v>
+        <v>3000</v>
       </c>
       <c r="AB8" s="0">
-        <v>93000</v>
+        <v>3000</v>
       </c>
       <c r="AC8" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦93,000.00</t>
+          <t>MONIEPOINT: ₦3,000.00</t>
         </is>
       </c>
       <c r="AD8" s="0" t="inlineStr">
         <is>
-          <t>BABA BALA</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="0">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>ELIZABETH EMBELLISHED</t>
+          <t>HOLLAND MEDIUM</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -834,16 +852,16 @@
         </is>
       </c>
       <c r="K9" s="0">
-        <v>38000</v>
+        <v>12000</v>
       </c>
       <c r="L9" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" s="0">
-        <v>114000</v>
+        <v>12000</v>
       </c>
       <c r="O9" s="0">
-        <v>114000</v>
+        <v>12000</v>
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
@@ -857,12 +875,12 @@
       </c>
       <c r="R9" s="0" t="inlineStr">
         <is>
-          <t>S5143 Edit S5143Clone</t>
+          <t>S5582 Edit S5582Clone</t>
         </is>
       </c>
       <c r="S9" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:18 pm</t>
+          <t>09/07/2026-01:32 pm</t>
         </is>
       </c>
       <c r="T9" s="0" t="inlineStr">
@@ -871,7 +889,7 @@
         </is>
       </c>
       <c r="U9" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V9" s="0" t="inlineStr">
         <is>
@@ -880,31 +898,36 @@
       </c>
       <c r="W9" s="0" t="inlineStr">
         <is>
-          <t>Jamila Wowplus </t>
+          <t>Abba Tahir Shop </t>
         </is>
       </c>
       <c r="Z9" s="0">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AA9" s="0">
-        <v>114000</v>
+        <v>12000</v>
       </c>
       <c r="AB9" s="0">
-        <v>114000</v>
+        <v>12000</v>
       </c>
       <c r="AC9" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦114,000.00</t>
+          <t>ACCESS BANK: ₦12,000.00</t>
+        </is>
+      </c>
+      <c r="AD9" s="0" t="inlineStr">
+        <is>
+          <t>HAJ HABIBA</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:31">
       <c r="A10" s="0">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>JULIUS HOLLAND PLAIN</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -918,16 +941,16 @@
         </is>
       </c>
       <c r="K10" s="0">
-        <v>17000</v>
+        <v>60000</v>
       </c>
       <c r="L10" s="0">
         <v>1</v>
       </c>
       <c r="N10" s="0">
-        <v>17000</v>
+        <v>60000</v>
       </c>
       <c r="O10" s="0">
-        <v>17000</v>
+        <v>60000</v>
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
@@ -941,12 +964,12 @@
       </c>
       <c r="R10" s="0" t="inlineStr">
         <is>
-          <t>S5144 Edit S5144Clone</t>
+          <t>S5583 Edit S5583Clone</t>
         </is>
       </c>
       <c r="S10" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:19 pm</t>
+          <t>09/07/2026-01:34 pm</t>
         </is>
       </c>
       <c r="T10" s="0" t="inlineStr">
@@ -964,31 +987,36 @@
       </c>
       <c r="W10" s="0" t="inlineStr">
         <is>
-          <t>NURHAF </t>
+          <t>Abba Tahir Shop </t>
         </is>
       </c>
       <c r="Z10" s="0">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="AA10" s="0">
-        <v>17000</v>
+        <v>60000</v>
       </c>
       <c r="AB10" s="0">
-        <v>17000</v>
+        <v>60000</v>
       </c>
       <c r="AC10" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦17,000.00</t>
+          <t>ACCESS BANK: ₦60,000.00</t>
+        </is>
+      </c>
+      <c r="AD10" s="0" t="inlineStr">
+        <is>
+          <t>SALISU GEEMAN</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:31">
       <c r="A11" s="0">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>Rotana holland</t>
+          <t>COTED'VIORE MEDIUM</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -998,20 +1026,20 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>YAYA SANI (3)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K11" s="0">
-        <v>8500</v>
+        <v>14500</v>
       </c>
       <c r="L11" s="0">
         <v>1</v>
       </c>
       <c r="N11" s="0">
-        <v>8500</v>
+        <v>14500</v>
       </c>
       <c r="O11" s="0">
-        <v>8500</v>
+        <v>14500</v>
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
@@ -1025,12 +1053,12 @@
       </c>
       <c r="R11" s="0" t="inlineStr">
         <is>
-          <t>S5145 Edit S5145Clone</t>
+          <t>S5584 Edit S5584Clone</t>
         </is>
       </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:19 pm</t>
+          <t>09/07/2026-01:49 pm</t>
         </is>
       </c>
       <c r="T11" s="0" t="inlineStr">
@@ -1039,7 +1067,7 @@
         </is>
       </c>
       <c r="U11" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V11" s="0" t="inlineStr">
         <is>
@@ -1048,31 +1076,31 @@
       </c>
       <c r="W11" s="0" t="inlineStr">
         <is>
-          <t>MARYAM TRENDY</t>
+          <t>Shamsu Shop </t>
         </is>
       </c>
       <c r="Z11" s="0">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="AA11" s="0">
-        <v>8500</v>
+        <v>38500</v>
       </c>
       <c r="AB11" s="0">
-        <v>8500</v>
+        <v>38500</v>
       </c>
       <c r="AC11" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦8,500.00</t>
+          <t>MONIEPOINT: ₦38,500.00</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:31">
       <c r="A12" s="0">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>HOLLANTEX </t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -1086,16 +1114,16 @@
         </is>
       </c>
       <c r="K12" s="0">
-        <v>19000</v>
+        <v>12000</v>
       </c>
       <c r="L12" s="0">
         <v>2</v>
       </c>
       <c r="N12" s="0">
-        <v>38000</v>
+        <v>24000</v>
       </c>
       <c r="O12" s="0">
-        <v>38000</v>
+        <v>24000</v>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
@@ -1109,12 +1137,12 @@
       </c>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t>S5146 Edit S5146Clone</t>
+          <t>S5584 Edit S5584Clone</t>
         </is>
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:23 pm</t>
+          <t>09/07/2026-01:49 pm</t>
         </is>
       </c>
       <c r="T12" s="0" t="inlineStr">
@@ -1123,7 +1151,7 @@
         </is>
       </c>
       <c r="U12" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V12" s="0" t="inlineStr">
         <is>
@@ -1132,31 +1160,31 @@
       </c>
       <c r="W12" s="0" t="inlineStr">
         <is>
-          <t>Haj Hadiza Pretty </t>
+          <t>Shamsu Shop </t>
         </is>
       </c>
       <c r="Z12" s="0">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA12" s="0">
-        <v>38000</v>
+        <v>38500</v>
       </c>
       <c r="AB12" s="0">
-        <v>38000</v>
+        <v>38500</v>
       </c>
       <c r="AC12" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦38,000.00</t>
+          <t>MONIEPOINT: ₦38,500.00</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:31">
       <c r="A13" s="0">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>BELLDAM</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -1170,16 +1198,16 @@
         </is>
       </c>
       <c r="K13" s="0">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="L13" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" s="0">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="O13" s="0">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
@@ -1193,12 +1221,12 @@
       </c>
       <c r="R13" s="0" t="inlineStr">
         <is>
-          <t>S5147 Edit S5147Clone</t>
+          <t>S5585 Edit S5585Clone</t>
         </is>
       </c>
       <c r="S13" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:24 pm</t>
+          <t>09/07/2026-03:40 pm</t>
         </is>
       </c>
       <c r="T13" s="0" t="inlineStr">
@@ -1207,7 +1235,7 @@
         </is>
       </c>
       <c r="U13" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V13" s="0" t="inlineStr">
         <is>
@@ -1216,36 +1244,36 @@
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z13" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA13" s="0">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="AB13" s="0">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="AC13" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦20,000.00</t>
+          <t>Cash: ₦15,000.00</t>
         </is>
       </c>
       <c r="AD13" s="0" t="inlineStr">
         <is>
-          <t>HAJ HABIBA ABDULQADIR</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:31">
       <c r="A14" s="0">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND PLAIN</t>
+          <t>CHIGANVY INDIA</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -1259,16 +1287,16 @@
         </is>
       </c>
       <c r="K14" s="0">
-        <v>175000</v>
+        <v>8000</v>
       </c>
       <c r="L14" s="0">
         <v>1</v>
       </c>
       <c r="N14" s="0">
-        <v>175000</v>
+        <v>8000</v>
       </c>
       <c r="O14" s="0">
-        <v>175000</v>
+        <v>8000</v>
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
@@ -1282,12 +1310,12 @@
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t>S5148 Edit S5148Clone</t>
+          <t>S5586 Edit S5586Clone</t>
         </is>
       </c>
       <c r="S14" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:25 pm</t>
+          <t>09/07/2026-04:59 pm</t>
         </is>
       </c>
       <c r="T14" s="0" t="inlineStr">
@@ -1296,7 +1324,7 @@
         </is>
       </c>
       <c r="U14" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V14" s="0" t="inlineStr">
         <is>
@@ -1305,36 +1333,36 @@
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z14" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA14" s="0">
-        <v>447000</v>
+        <v>8000</v>
       </c>
       <c r="AB14" s="0">
-        <v>447000</v>
+        <v>8000</v>
       </c>
       <c r="AC14" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦447,000.00</t>
+          <t>MONIEPOINT: ₦8,000.00</t>
         </is>
       </c>
       <c r="AD14" s="0" t="inlineStr">
         <is>
-          <t>HAJ KHADIJA</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:31">
       <c r="A15" s="0">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>JULIUS CRYSTAL SHINE</t>
+          <t>GLORY WAX</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -1348,16 +1376,16 @@
         </is>
       </c>
       <c r="K15" s="0">
-        <v>95000</v>
+        <v>10000</v>
       </c>
       <c r="L15" s="0">
         <v>2</v>
       </c>
       <c r="N15" s="0">
-        <v>190000</v>
+        <v>20000</v>
       </c>
       <c r="O15" s="0">
-        <v>190000</v>
+        <v>20000</v>
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
@@ -1371,12 +1399,12 @@
       </c>
       <c r="R15" s="0" t="inlineStr">
         <is>
-          <t>S5148 Edit S5148Clone</t>
+          <t>S5587 Edit S5587Clone</t>
         </is>
       </c>
       <c r="S15" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:25 pm</t>
+          <t>09/07/2026-05:27 pm</t>
         </is>
       </c>
       <c r="T15" s="0" t="inlineStr">
@@ -1385,7 +1413,7 @@
         </is>
       </c>
       <c r="U15" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V15" s="0" t="inlineStr">
         <is>
@@ -1394,36 +1422,36 @@
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>Fahad Tahir </t>
         </is>
       </c>
       <c r="Z15" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA15" s="0">
-        <v>447000</v>
+        <v>101500</v>
       </c>
       <c r="AB15" s="0">
-        <v>447000</v>
+        <v>101500</v>
       </c>
       <c r="AC15" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦447,000.00</t>
+          <t>Store Account: ₦101,500.00</t>
         </is>
       </c>
       <c r="AD15" s="0" t="inlineStr">
         <is>
-          <t>HAJ KHADIJA</t>
+          <t>RABI NIGER</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:31">
       <c r="A16" s="0">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>JULIUS EMBELLISHED </t>
+          <t>Fantastic Holland</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -1433,20 +1461,20 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>YAYA SANI (3)</t>
         </is>
       </c>
       <c r="K16" s="0">
-        <v>82000</v>
+        <v>8500</v>
       </c>
       <c r="L16" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N16" s="0">
-        <v>82000</v>
+        <v>42500</v>
       </c>
       <c r="O16" s="0">
-        <v>82000</v>
+        <v>42500</v>
       </c>
       <c r="P16" s="0" t="inlineStr">
         <is>
@@ -1460,12 +1488,12 @@
       </c>
       <c r="R16" s="0" t="inlineStr">
         <is>
-          <t>S5148 Edit S5148Clone</t>
+          <t>S5587 Edit S5587Clone</t>
         </is>
       </c>
       <c r="S16" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:25 pm</t>
+          <t>09/07/2026-05:27 pm</t>
         </is>
       </c>
       <c r="T16" s="0" t="inlineStr">
@@ -1474,7 +1502,7 @@
         </is>
       </c>
       <c r="U16" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V16" s="0" t="inlineStr">
         <is>
@@ -1483,36 +1511,36 @@
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>Fahad Tahir </t>
         </is>
       </c>
       <c r="Z16" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA16" s="0">
-        <v>447000</v>
+        <v>101500</v>
       </c>
       <c r="AB16" s="0">
-        <v>447000</v>
+        <v>101500</v>
       </c>
       <c r="AC16" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦447,000.00</t>
+          <t>Store Account: ₦101,500.00</t>
         </is>
       </c>
       <c r="AD16" s="0" t="inlineStr">
         <is>
-          <t>HAJ KHADIJA</t>
+          <t>RABI NIGER</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:31">
       <c r="A17" s="0">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>GRANDEUR PLAIN</t>
+          <t>Adire Fashion</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -1522,20 +1550,20 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>HAFIZU TAHIR SHOP (5)</t>
         </is>
       </c>
       <c r="K17" s="0">
-        <v>23000</v>
+        <v>13000</v>
       </c>
       <c r="L17" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17" s="0">
-        <v>23000</v>
+        <v>39000</v>
       </c>
       <c r="O17" s="0">
-        <v>23000</v>
+        <v>39000</v>
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
@@ -1549,12 +1577,12 @@
       </c>
       <c r="R17" s="0" t="inlineStr">
         <is>
-          <t>S5149 Edit S5149Clone</t>
+          <t>S5587 Edit S5587Clone</t>
         </is>
       </c>
       <c r="S17" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:25 pm</t>
+          <t>09/07/2026-05:27 pm</t>
         </is>
       </c>
       <c r="T17" s="0" t="inlineStr">
@@ -1563,7 +1591,7 @@
         </is>
       </c>
       <c r="U17" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V17" s="0" t="inlineStr">
         <is>
@@ -1572,31 +1600,36 @@
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
-          <t>HAJ HAJARA GOMBE</t>
+          <t>Fahad Tahir </t>
         </is>
       </c>
       <c r="Z17" s="0">
-        <v>209</v>
+        <v>22</v>
       </c>
       <c r="AA17" s="0">
-        <v>23000</v>
+        <v>101500</v>
       </c>
       <c r="AB17" s="0">
-        <v>23000</v>
+        <v>101500</v>
       </c>
       <c r="AC17" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦23,000.00</t>
+          <t>Store Account: ₦101,500.00</t>
+        </is>
+      </c>
+      <c r="AD17" s="0" t="inlineStr">
+        <is>
+          <t>RABI NIGER</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:31">
       <c r="A18" s="0">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>HIGHTEST</t>
+          <t>ELIZABETH EMBELLISHED</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -1610,16 +1643,16 @@
         </is>
       </c>
       <c r="K18" s="0">
-        <v>10500</v>
+        <v>40000</v>
       </c>
       <c r="L18" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" s="0">
-        <v>21000</v>
+        <v>40000</v>
       </c>
       <c r="O18" s="0">
-        <v>21000</v>
+        <v>40000</v>
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
@@ -1633,12 +1666,12 @@
       </c>
       <c r="R18" s="0" t="inlineStr">
         <is>
-          <t>S5150 Edit S5150Clone</t>
+          <t>S5588 Edit S5588Clone</t>
         </is>
       </c>
       <c r="S18" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:26 pm</t>
+          <t>09/07/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T18" s="0" t="inlineStr">
@@ -1647,7 +1680,7 @@
         </is>
       </c>
       <c r="U18" s="0">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="V18" s="0" t="inlineStr">
         <is>
@@ -1656,41 +1689,36 @@
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>UMMI KATSINA </t>
         </is>
       </c>
       <c r="Z18" s="0">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="AA18" s="0">
-        <v>21000</v>
+        <v>333500</v>
       </c>
       <c r="AB18" s="0">
-        <v>21000</v>
+        <v>333500</v>
       </c>
       <c r="AC18" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦21,000.00</t>
-        </is>
-      </c>
-      <c r="AD18" s="0" t="inlineStr">
-        <is>
-          <t>ALE MANSUR</t>
+          <t>Store Account: ₦333,500.00</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:31">
       <c r="A19" s="0">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>MOONLIGHT AND SUPREME FOLDER</t>
+          <t>LATEST ULTRA EMBELLISHED </t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G19" s="0" t="inlineStr">
@@ -1699,16 +1727,16 @@
         </is>
       </c>
       <c r="K19" s="0">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="L19" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N19" s="0">
-        <v>54000</v>
+        <v>40000</v>
       </c>
       <c r="O19" s="0">
-        <v>54000</v>
+        <v>40000</v>
       </c>
       <c r="P19" s="0" t="inlineStr">
         <is>
@@ -1722,12 +1750,12 @@
       </c>
       <c r="R19" s="0" t="inlineStr">
         <is>
-          <t>S5151 Edit S5151Clone</t>
+          <t>S5588 Edit S5588Clone</t>
         </is>
       </c>
       <c r="S19" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:28 pm</t>
+          <t>09/07/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T19" s="0" t="inlineStr">
@@ -1736,7 +1764,7 @@
         </is>
       </c>
       <c r="U19" s="0">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="V19" s="0" t="inlineStr">
         <is>
@@ -1745,36 +1773,36 @@
       </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
-          <t>HAJ AMINA SOKOTO </t>
+          <t>UMMI KATSINA </t>
         </is>
       </c>
       <c r="Z19" s="0">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AA19" s="0">
-        <v>104000</v>
+        <v>333500</v>
       </c>
       <c r="AB19" s="0">
-        <v>104000</v>
+        <v>333500</v>
       </c>
       <c r="AC19" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦104,000.00</t>
+          <t>Store Account: ₦333,500.00</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:31">
       <c r="A20" s="0">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>RIGHTMAN AND WISEMAN</t>
+          <t>HOLLAND MEDIUM</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
@@ -1783,16 +1811,16 @@
         </is>
       </c>
       <c r="K20" s="0">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="L20" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N20" s="0">
-        <v>50000</v>
+        <v>72000</v>
       </c>
       <c r="O20" s="0">
-        <v>50000</v>
+        <v>72000</v>
       </c>
       <c r="P20" s="0" t="inlineStr">
         <is>
@@ -1806,12 +1834,12 @@
       </c>
       <c r="R20" s="0" t="inlineStr">
         <is>
-          <t>S5151 Edit S5151Clone</t>
+          <t>S5588 Edit S5588Clone</t>
         </is>
       </c>
       <c r="S20" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:28 pm</t>
+          <t>09/07/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T20" s="0" t="inlineStr">
@@ -1820,7 +1848,7 @@
         </is>
       </c>
       <c r="U20" s="0">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="V20" s="0" t="inlineStr">
         <is>
@@ -1829,31 +1857,31 @@
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>HAJ AMINA SOKOTO </t>
+          <t>UMMI KATSINA </t>
         </is>
       </c>
       <c r="Z20" s="0">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AA20" s="0">
-        <v>104000</v>
+        <v>333500</v>
       </c>
       <c r="AB20" s="0">
-        <v>104000</v>
+        <v>333500</v>
       </c>
       <c r="AC20" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦104,000.00</t>
+          <t>Store Account: ₦333,500.00</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:31">
       <c r="A21" s="0">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTEX EMBELLISHED</t>
+          <t>BELLDAM</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -1867,16 +1895,16 @@
         </is>
       </c>
       <c r="K21" s="0">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="L21" s="0">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N21" s="0">
-        <v>18000</v>
+        <v>35000</v>
       </c>
       <c r="O21" s="0">
-        <v>18000</v>
+        <v>35000</v>
       </c>
       <c r="P21" s="0" t="inlineStr">
         <is>
@@ -1890,12 +1918,12 @@
       </c>
       <c r="R21" s="0" t="inlineStr">
         <is>
-          <t>S5152 Edit S5152Clone</t>
+          <t>S5588 Edit S5588Clone</t>
         </is>
       </c>
       <c r="S21" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:29 pm</t>
+          <t>09/07/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T21" s="0" t="inlineStr">
@@ -1904,7 +1932,7 @@
         </is>
       </c>
       <c r="U21" s="0">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V21" s="0" t="inlineStr">
         <is>
@@ -1913,36 +1941,31 @@
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>UMMI KATSINA </t>
         </is>
       </c>
       <c r="Z21" s="0">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="AA21" s="0">
-        <v>18000</v>
+        <v>333500</v>
       </c>
       <c r="AB21" s="0">
-        <v>18000</v>
+        <v>333500</v>
       </c>
       <c r="AC21" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦18,000.00</t>
-        </is>
-      </c>
-      <c r="AD21" s="0" t="inlineStr">
-        <is>
-          <t>MARYAM</t>
+          <t>Store Account: ₦333,500.00</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:31">
       <c r="A22" s="0">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>Hollantex Mix pattern</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -1956,16 +1979,16 @@
         </is>
       </c>
       <c r="K22" s="0">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="L22" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N22" s="0">
-        <v>18000</v>
+        <v>62500</v>
       </c>
       <c r="O22" s="0">
-        <v>18000</v>
+        <v>62500</v>
       </c>
       <c r="P22" s="0" t="inlineStr">
         <is>
@@ -1979,12 +2002,12 @@
       </c>
       <c r="R22" s="0" t="inlineStr">
         <is>
-          <t>S5153 Edit S5153Clone</t>
+          <t>S5588 Edit S5588Clone</t>
         </is>
       </c>
       <c r="S22" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:29 pm</t>
+          <t>09/07/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T22" s="0" t="inlineStr">
@@ -1993,7 +2016,7 @@
         </is>
       </c>
       <c r="U22" s="0">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V22" s="0" t="inlineStr">
         <is>
@@ -2002,36 +2025,31 @@
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>UMMI KATSINA </t>
         </is>
       </c>
       <c r="Z22" s="0">
-        <v>23</v>
+        <v>341</v>
       </c>
       <c r="AA22" s="0">
-        <v>18000</v>
+        <v>333500</v>
       </c>
       <c r="AB22" s="0">
-        <v>18000</v>
+        <v>333500</v>
       </c>
       <c r="AC22" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦18,000.00</t>
-        </is>
-      </c>
-      <c r="AD22" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦333,500.00</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:31">
       <c r="A23" s="0">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>Magic holland</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -2041,20 +2059,20 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>YAYA SANI (3)</t>
         </is>
       </c>
       <c r="K23" s="0">
-        <v>17000</v>
+        <v>10500</v>
       </c>
       <c r="L23" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N23" s="0">
-        <v>68000</v>
+        <v>84000</v>
       </c>
       <c r="O23" s="0">
-        <v>68000</v>
+        <v>84000</v>
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
@@ -2068,12 +2086,12 @@
       </c>
       <c r="R23" s="0" t="inlineStr">
         <is>
-          <t>S5154 Edit S5154Clone</t>
+          <t>S5588 Edit S5588Clone</t>
         </is>
       </c>
       <c r="S23" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:29 pm</t>
+          <t>09/07/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T23" s="0" t="inlineStr">
@@ -2082,7 +2100,7 @@
         </is>
       </c>
       <c r="U23" s="0">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="V23" s="0" t="inlineStr">
         <is>
@@ -2091,41 +2109,36 @@
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>UMMI KATSINA </t>
         </is>
       </c>
       <c r="Z23" s="0">
-        <v>23</v>
+        <v>341</v>
       </c>
       <c r="AA23" s="0">
-        <v>68000</v>
+        <v>333500</v>
       </c>
       <c r="AB23" s="0">
-        <v>68000</v>
+        <v>333500</v>
       </c>
       <c r="AC23" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦68,000.00</t>
-        </is>
-      </c>
-      <c r="AD23" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦333,500.00</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:31">
       <c r="A24" s="0">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA A</t>
+          <t>ABS MAITABARMA</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
@@ -2134,16 +2147,16 @@
         </is>
       </c>
       <c r="K24" s="0">
-        <v>57000</v>
+        <v>33000</v>
       </c>
       <c r="L24" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N24" s="0">
-        <v>57000</v>
+        <v>99000</v>
       </c>
       <c r="O24" s="0">
-        <v>57000</v>
+        <v>99000</v>
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
@@ -2157,12 +2170,12 @@
       </c>
       <c r="R24" s="0" t="inlineStr">
         <is>
-          <t>S5155 Edit S5155Clone</t>
+          <t>S5589 Edit S5589Clone</t>
         </is>
       </c>
       <c r="S24" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:30 pm</t>
+          <t>09/07/2026-05:30 pm</t>
         </is>
       </c>
       <c r="T24" s="0" t="inlineStr">
@@ -2171,7 +2184,7 @@
         </is>
       </c>
       <c r="U24" s="0">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="V24" s="0" t="inlineStr">
         <is>
@@ -2180,36 +2193,36 @@
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>Fahad Tahir </t>
         </is>
       </c>
       <c r="Z24" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA24" s="0">
-        <v>57000</v>
+        <v>299000</v>
       </c>
       <c r="AB24" s="0">
-        <v>57000</v>
+        <v>299000</v>
       </c>
       <c r="AC24" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦57,000.00</t>
+          <t>Store Account: ₦299,000.00</t>
         </is>
       </c>
       <c r="AD24" s="0" t="inlineStr">
         <is>
-          <t>KOLLERAM</t>
+          <t>AUNTY AISHA MAIDUGURI</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:31">
       <c r="A25" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>HOLLAND MEDIUM</t>
+          <t>HOLLANTEX </t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
@@ -2226,13 +2239,13 @@
         <v>12000</v>
       </c>
       <c r="L25" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N25" s="0">
-        <v>24000</v>
+        <v>96000</v>
       </c>
       <c r="O25" s="0">
-        <v>24000</v>
+        <v>96000</v>
       </c>
       <c r="P25" s="0" t="inlineStr">
         <is>
@@ -2246,12 +2259,12 @@
       </c>
       <c r="R25" s="0" t="inlineStr">
         <is>
-          <t>S5156 Edit S5156Clone</t>
+          <t>S5589 Edit S5589Clone</t>
         </is>
       </c>
       <c r="S25" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:32 pm</t>
+          <t>09/07/2026-05:30 pm</t>
         </is>
       </c>
       <c r="T25" s="0" t="inlineStr">
@@ -2260,7 +2273,7 @@
         </is>
       </c>
       <c r="U25" s="0">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="V25" s="0" t="inlineStr">
         <is>
@@ -2269,36 +2282,36 @@
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>Fahad Tahir </t>
         </is>
       </c>
       <c r="Z25" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA25" s="0">
-        <v>24000</v>
+        <v>299000</v>
       </c>
       <c r="AB25" s="0">
-        <v>24000</v>
+        <v>299000</v>
       </c>
       <c r="AC25" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦24,000.00</t>
+          <t>Store Account: ₦299,000.00</t>
         </is>
       </c>
       <c r="AD25" s="0" t="inlineStr">
         <is>
-          <t>CTM</t>
+          <t>AUNTY AISHA MAIDUGURI</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:31">
       <c r="A26" s="0">
-        <v>117</v>
+        <v>212</v>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>Adire Fashion</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -2308,20 +2321,20 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>HAFIZU TAHIR SHOP (5)</t>
         </is>
       </c>
       <c r="K26" s="0">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="L26" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N26" s="0">
-        <v>85000</v>
+        <v>104000</v>
       </c>
       <c r="O26" s="0">
-        <v>85000</v>
+        <v>104000</v>
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
@@ -2335,12 +2348,12 @@
       </c>
       <c r="R26" s="0" t="inlineStr">
         <is>
-          <t>S5157 Edit S5157Clone</t>
+          <t>S5589 Edit S5589Clone</t>
         </is>
       </c>
       <c r="S26" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:33 pm</t>
+          <t>09/07/2026-05:30 pm</t>
         </is>
       </c>
       <c r="T26" s="0" t="inlineStr">
@@ -2349,7 +2362,7 @@
         </is>
       </c>
       <c r="U26" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V26" s="0" t="inlineStr">
         <is>
@@ -2358,36 +2371,36 @@
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>Fahad Tahir </t>
         </is>
       </c>
       <c r="Z26" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA26" s="0">
-        <v>85000</v>
+        <v>299000</v>
       </c>
       <c r="AB26" s="0">
-        <v>85000</v>
+        <v>299000</v>
       </c>
       <c r="AC26" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦85,000.00</t>
+          <t>Store Account: ₦299,000.00</t>
         </is>
       </c>
       <c r="AD26" s="0" t="inlineStr">
         <is>
-          <t>UMAR ONLINE</t>
+          <t>AUNTY AISHA MAIDUGURI</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:31">
       <c r="A27" s="0">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY GOLD</t>
+          <t>ELIZABETH EMBELLISHED</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -2401,16 +2414,16 @@
         </is>
       </c>
       <c r="K27" s="0">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="L27" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N27" s="0">
-        <v>72000</v>
+        <v>39000</v>
       </c>
       <c r="O27" s="0">
-        <v>72000</v>
+        <v>39000</v>
       </c>
       <c r="P27" s="0" t="inlineStr">
         <is>
@@ -2424,12 +2437,12 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>S5158 Edit S5158Clone</t>
+          <t>S5590 Edit S5590Clone</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:34 pm</t>
+          <t>09/07/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T27" s="0" t="inlineStr">
@@ -2438,7 +2451,7 @@
         </is>
       </c>
       <c r="U27" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V27" s="0" t="inlineStr">
         <is>
@@ -2454,14 +2467,14 @@
         <v>23</v>
       </c>
       <c r="AA27" s="0">
-        <v>72000</v>
+        <v>216000</v>
       </c>
       <c r="AB27" s="0">
-        <v>72000</v>
+        <v>216000</v>
       </c>
       <c r="AC27" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦72,000.00</t>
+          <t>MONIEPOINT: ₦216,000.00</t>
         </is>
       </c>
       <c r="AD27" s="0" t="inlineStr">
@@ -2472,11 +2485,11 @@
     </row>
     <row r="28" spans="1:31">
       <c r="A28" s="0">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA LACE</t>
+          <t>LATEST ULTRA EMBELLISHED </t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
@@ -2490,16 +2503,16 @@
         </is>
       </c>
       <c r="K28" s="0">
-        <v>73000</v>
+        <v>39000</v>
       </c>
       <c r="L28" s="0">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="0">
-        <v>-73000</v>
+        <v>78000</v>
       </c>
       <c r="O28" s="0">
-        <v>-73000</v>
+        <v>78000</v>
       </c>
       <c r="P28" s="0" t="inlineStr">
         <is>
@@ -2513,12 +2526,12 @@
       </c>
       <c r="R28" s="0" t="inlineStr">
         <is>
-          <t>S5159 Edit S5159Clone</t>
+          <t>S5590 Edit S5590Clone</t>
         </is>
       </c>
       <c r="S28" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:35 pm</t>
+          <t>09/07/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T28" s="0" t="inlineStr">
@@ -2526,10 +2539,8 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="U28" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="U28" s="0">
+        <v>9</v>
       </c>
       <c r="V28" s="0" t="inlineStr">
         <is>
@@ -2538,31 +2549,36 @@
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>Waleed Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z28" s="0">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA28" s="0">
-        <v>10000</v>
+        <v>216000</v>
       </c>
       <c r="AB28" s="0">
-        <v>10000</v>
+        <v>216000</v>
       </c>
       <c r="AC28" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦10,000.00</t>
+          <t>MONIEPOINT: ₦216,000.00</t>
+        </is>
+      </c>
+      <c r="AD28" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:31">
       <c r="A29" s="0">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>JULIUS EMBELLISHED </t>
+          <t>EMBELLISHED MDT</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -2576,16 +2592,16 @@
         </is>
       </c>
       <c r="K29" s="0">
-        <v>83000</v>
+        <v>17500</v>
       </c>
       <c r="L29" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N29" s="0">
-        <v>83000</v>
+        <v>70000</v>
       </c>
       <c r="O29" s="0">
-        <v>83000</v>
+        <v>70000</v>
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
@@ -2599,12 +2615,12 @@
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t>S5159 Edit S5159Clone</t>
+          <t>S5590 Edit S5590Clone</t>
         </is>
       </c>
       <c r="S29" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:35 pm</t>
+          <t>09/07/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T29" s="0" t="inlineStr">
@@ -2612,10 +2628,8 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="U29" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="U29" s="0">
+        <v>9</v>
       </c>
       <c r="V29" s="0" t="inlineStr">
         <is>
@@ -2624,31 +2638,36 @@
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>Waleed Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z29" s="0">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA29" s="0">
-        <v>10000</v>
+        <v>216000</v>
       </c>
       <c r="AB29" s="0">
-        <v>10000</v>
+        <v>216000</v>
       </c>
       <c r="AC29" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦10,000.00</t>
+          <t>MONIEPOINT: ₦216,000.00</t>
+        </is>
+      </c>
+      <c r="AD29" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:31">
       <c r="A30" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>PRESTIGE EMBELLISHED</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
@@ -2662,16 +2681,16 @@
         </is>
       </c>
       <c r="K30" s="0">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="L30" s="0">
         <v>1</v>
       </c>
       <c r="N30" s="0">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="O30" s="0">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="P30" s="0" t="inlineStr">
         <is>
@@ -2685,12 +2704,12 @@
       </c>
       <c r="R30" s="0" t="inlineStr">
         <is>
-          <t>S5160 Edit S5160Clone</t>
+          <t>S5590 Edit S5590Clone</t>
         </is>
       </c>
       <c r="S30" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-05:35 pm</t>
+          <t>09/07/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T30" s="0" t="inlineStr">
@@ -2699,7 +2718,7 @@
         </is>
       </c>
       <c r="U30" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V30" s="0" t="inlineStr">
         <is>
@@ -2715,14 +2734,14 @@
         <v>23</v>
       </c>
       <c r="AA30" s="0">
-        <v>17500</v>
+        <v>216000</v>
       </c>
       <c r="AB30" s="0">
-        <v>17500</v>
+        <v>216000</v>
       </c>
       <c r="AC30" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦17,500.00</t>
+          <t>MONIEPOINT: ₦216,000.00</t>
         </is>
       </c>
       <c r="AD30" s="0" t="inlineStr">
@@ -2733,11 +2752,11 @@
     </row>
     <row r="31" spans="1:31">
       <c r="A31" s="0">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>Adire Fashion</t>
+          <t>HOLLAND MEDIUM</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
@@ -2747,20 +2766,20 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K31" s="0">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="L31" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31" s="0">
-        <v>25000</v>
+        <v>12000</v>
       </c>
       <c r="O31" s="0">
-        <v>25000</v>
+        <v>12000</v>
       </c>
       <c r="P31" s="0" t="inlineStr">
         <is>
@@ -2774,12 +2793,12 @@
       </c>
       <c r="R31" s="0" t="inlineStr">
         <is>
-          <t>S5161 Edit S5161Clone</t>
+          <t>S5590 Edit S5590Clone</t>
         </is>
       </c>
       <c r="S31" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-06:15 pm</t>
+          <t>09/07/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T31" s="0" t="inlineStr">
@@ -2788,7 +2807,7 @@
         </is>
       </c>
       <c r="U31" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V31" s="0" t="inlineStr">
         <is>
@@ -2797,31 +2816,36 @@
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>Shamsu Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z31" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA31" s="0">
-        <v>25000</v>
+        <v>216000</v>
       </c>
       <c r="AB31" s="0">
-        <v>25000</v>
+        <v>216000</v>
       </c>
       <c r="AC31" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦25,000.00</t>
+          <t>MONIEPOINT: ₦216,000.00</t>
+        </is>
+      </c>
+      <c r="AD31" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:31">
       <c r="A32" s="0">
-        <v>119</v>
+        <v>212</v>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>Adire Fashion</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
@@ -2831,20 +2855,20 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>HAFIZU TAHIR SHOP (5)</t>
         </is>
       </c>
       <c r="K32" s="0">
-        <v>15500</v>
+        <v>12500</v>
       </c>
       <c r="L32" s="0">
         <v>1</v>
       </c>
       <c r="N32" s="0">
-        <v>15500</v>
+        <v>12500</v>
       </c>
       <c r="O32" s="0">
-        <v>15500</v>
+        <v>12500</v>
       </c>
       <c r="P32" s="0" t="inlineStr">
         <is>
@@ -2858,12 +2882,12 @@
       </c>
       <c r="R32" s="0" t="inlineStr">
         <is>
-          <t>S5162 Edit S5162Clone</t>
+          <t>S5591 Edit S5591Clone</t>
         </is>
       </c>
       <c r="S32" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-06:16 pm</t>
+          <t>09/07/2026-05:47 pm</t>
         </is>
       </c>
       <c r="T32" s="0" t="inlineStr">
@@ -2881,31 +2905,36 @@
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>Khalid Abasu Kala  </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z32" s="0">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="AA32" s="0">
-        <v>15500</v>
+        <v>12500</v>
       </c>
       <c r="AB32" s="0">
-        <v>15500</v>
+        <v>12500</v>
       </c>
       <c r="AC32" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦15,500.00</t>
+          <t>MONIEPOINT: ₦12,500.00</t>
+        </is>
+      </c>
+      <c r="AD32" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:31">
       <c r="A33" s="0">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>LATEST ULTRA EMBELLISHED </t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
@@ -2919,10 +2948,10 @@
         </is>
       </c>
       <c r="K33" s="0">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="L33" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" s="0">
         <v>40000</v>
@@ -2942,12 +2971,12 @@
       </c>
       <c r="R33" s="0" t="inlineStr">
         <is>
-          <t>S5163 Edit S5163Clone</t>
+          <t>S5592 Edit S5592Clone</t>
         </is>
       </c>
       <c r="S33" s="0" t="inlineStr">
         <is>
-          <t>08/26/2026-06:16 pm</t>
+          <t>09/07/2026-05:49 pm</t>
         </is>
       </c>
       <c r="T33" s="0" t="inlineStr">
@@ -2956,7 +2985,7 @@
         </is>
       </c>
       <c r="U33" s="0">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="V33" s="0" t="inlineStr">
         <is>
@@ -2965,21 +2994,25 @@
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>HAJ MAIMUNA ZANGO </t>
+          <t>HAJ LADIDI </t>
         </is>
       </c>
       <c r="Z33" s="0">
-        <v>336</v>
-      </c>
-      <c r="AA33" s="0">
-        <v>40000</v>
-      </c>
-      <c r="AB33" s="0">
-        <v>40000</v>
+        <v>127</v>
+      </c>
+      <c r="AA33" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB33" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
       </c>
       <c r="AC33" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦40,000.00</t>
+          <t>Store Account: ₦0.00</t>
         </is>
       </c>
     </row>
@@ -3003,72 +3036,1786 @@
         </is>
       </c>
       <c r="K34" s="0">
+        <v>20000</v>
+      </c>
+      <c r="L34" s="0">
+        <v>-2</v>
+      </c>
+      <c r="N34" s="0">
+        <v>-40000</v>
+      </c>
+      <c r="O34" s="0">
+        <v>-40000</v>
+      </c>
+      <c r="P34" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q34" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R34" s="0" t="inlineStr">
+        <is>
+          <t>S5592 Edit S5592Clone</t>
+        </is>
+      </c>
+      <c r="S34" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:49 pm</t>
+        </is>
+      </c>
+      <c r="T34" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U34" s="0">
+        <v>-1</v>
+      </c>
+      <c r="V34" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W34" s="0" t="inlineStr">
+        <is>
+          <t>HAJ LADIDI </t>
+        </is>
+      </c>
+      <c r="Z34" s="0">
+        <v>127</v>
+      </c>
+      <c r="AA34" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB34" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AC34" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:31">
+      <c r="A35" s="0">
+        <v>105</v>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY GOLD</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K35" s="0">
+        <v>25000</v>
+      </c>
+      <c r="L35" s="0">
+        <v>1</v>
+      </c>
+      <c r="N35" s="0">
+        <v>25000</v>
+      </c>
+      <c r="O35" s="0">
+        <v>25000</v>
+      </c>
+      <c r="P35" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q35" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R35" s="0" t="inlineStr">
+        <is>
+          <t>S5593 Edit S5593Clone</t>
+        </is>
+      </c>
+      <c r="S35" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:50 pm</t>
+        </is>
+      </c>
+      <c r="T35" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U35" s="0">
+        <v>6</v>
+      </c>
+      <c r="V35" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W35" s="0" t="inlineStr">
+        <is>
+          <t>RUKAYYA NASIR</t>
+        </is>
+      </c>
+      <c r="Z35" s="0">
+        <v>188</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AB35" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AC35" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦114,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:31">
+      <c r="A36" s="0">
+        <v>111</v>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>FULL STONE EMBELLISHED </t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K36" s="0">
+        <v>20000</v>
+      </c>
+      <c r="L36" s="0">
+        <v>1</v>
+      </c>
+      <c r="N36" s="0">
+        <v>20000</v>
+      </c>
+      <c r="O36" s="0">
+        <v>20000</v>
+      </c>
+      <c r="P36" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q36" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R36" s="0" t="inlineStr">
+        <is>
+          <t>S5593 Edit S5593Clone</t>
+        </is>
+      </c>
+      <c r="S36" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:50 pm</t>
+        </is>
+      </c>
+      <c r="T36" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U36" s="0">
+        <v>6</v>
+      </c>
+      <c r="V36" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W36" s="0" t="inlineStr">
+        <is>
+          <t>RUKAYYA NASIR</t>
+        </is>
+      </c>
+      <c r="Z36" s="0">
+        <v>188</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AC36" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦114,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:31">
+      <c r="A37" s="0">
+        <v>117</v>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>EMBELLISHED MDT</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K37" s="0">
+        <v>18000</v>
+      </c>
+      <c r="L37" s="0">
+        <v>1</v>
+      </c>
+      <c r="N37" s="0">
+        <v>18000</v>
+      </c>
+      <c r="O37" s="0">
+        <v>18000</v>
+      </c>
+      <c r="P37" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q37" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R37" s="0" t="inlineStr">
+        <is>
+          <t>S5593 Edit S5593Clone</t>
+        </is>
+      </c>
+      <c r="S37" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:50 pm</t>
+        </is>
+      </c>
+      <c r="T37" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U37" s="0">
+        <v>6</v>
+      </c>
+      <c r="V37" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W37" s="0" t="inlineStr">
+        <is>
+          <t>RUKAYYA NASIR</t>
+        </is>
+      </c>
+      <c r="Z37" s="0">
+        <v>188</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AC37" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦114,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:31">
+      <c r="A38" s="0">
+        <v>118</v>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>PRESTIGE EMBELLISHED</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K38" s="0">
+        <v>17000</v>
+      </c>
+      <c r="L38" s="0">
+        <v>3</v>
+      </c>
+      <c r="N38" s="0">
+        <v>51000</v>
+      </c>
+      <c r="O38" s="0">
+        <v>51000</v>
+      </c>
+      <c r="P38" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q38" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R38" s="0" t="inlineStr">
+        <is>
+          <t>S5593 Edit S5593Clone</t>
+        </is>
+      </c>
+      <c r="S38" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:50 pm</t>
+        </is>
+      </c>
+      <c r="T38" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U38" s="0">
+        <v>6</v>
+      </c>
+      <c r="V38" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W38" s="0" t="inlineStr">
+        <is>
+          <t>RUKAYYA NASIR</t>
+        </is>
+      </c>
+      <c r="Z38" s="0">
+        <v>188</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>114000</v>
+      </c>
+      <c r="AC38" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦114,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:31">
+      <c r="A39" s="0">
+        <v>106</v>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY COTONOU PLAIN</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K39" s="0">
         <v>19000</v>
       </c>
-      <c r="L34" s="0">
+      <c r="L39" s="0">
+        <v>1</v>
+      </c>
+      <c r="N39" s="0">
+        <v>19000</v>
+      </c>
+      <c r="O39" s="0">
+        <v>19000</v>
+      </c>
+      <c r="P39" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q39" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R39" s="0" t="inlineStr">
+        <is>
+          <t>S5594 Edit S5594Clone</t>
+        </is>
+      </c>
+      <c r="S39" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:50 pm</t>
+        </is>
+      </c>
+      <c r="T39" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U39" s="0">
+        <v>1</v>
+      </c>
+      <c r="V39" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W39" s="0" t="inlineStr">
+        <is>
+          <t>Jamila Baba </t>
+        </is>
+      </c>
+      <c r="Z39" s="0">
+        <v>38</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>19000</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>19000</v>
+      </c>
+      <c r="AC39" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦19,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
+      <c r="A40" s="0">
+        <v>137</v>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>SUPER FAMOUS</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K40" s="0">
+        <v>9500</v>
+      </c>
+      <c r="L40" s="0">
+        <v>21</v>
+      </c>
+      <c r="N40" s="0">
+        <v>199500</v>
+      </c>
+      <c r="O40" s="0">
+        <v>199500</v>
+      </c>
+      <c r="P40" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q40" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R40" s="0" t="inlineStr">
+        <is>
+          <t>S5595 Edit S5595Clone</t>
+        </is>
+      </c>
+      <c r="S40" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:51 pm</t>
+        </is>
+      </c>
+      <c r="T40" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U40" s="0">
+        <v>21</v>
+      </c>
+      <c r="V40" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W40" s="0" t="inlineStr">
+        <is>
+          <t>NURHAF </t>
+        </is>
+      </c>
+      <c r="Z40" s="0">
+        <v>33</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>199500</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>199500</v>
+      </c>
+      <c r="AC40" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦199,500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:31">
+      <c r="A41" s="0">
+        <v>141</v>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>BELLDAM</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K41" s="0">
+        <v>4900</v>
+      </c>
+      <c r="L41" s="0">
+        <v>1</v>
+      </c>
+      <c r="N41" s="0">
+        <v>4900</v>
+      </c>
+      <c r="O41" s="0">
+        <v>4900</v>
+      </c>
+      <c r="P41" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q41" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R41" s="0" t="inlineStr">
+        <is>
+          <t>S5596 Edit S5596Clone</t>
+        </is>
+      </c>
+      <c r="S41" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:51 pm</t>
+        </is>
+      </c>
+      <c r="T41" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U41" s="0">
+        <v>3</v>
+      </c>
+      <c r="V41" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W41" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Walk-in Customers </t>
+        </is>
+      </c>
+      <c r="Z41" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>10500</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>10500</v>
+      </c>
+      <c r="AC41" s="0" t="inlineStr">
+        <is>
+          <t>Cash: ₦10,500.00</t>
+        </is>
+      </c>
+      <c r="AD41" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:31">
+      <c r="A42" s="0">
+        <v>143</v>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>ROBA ATAMPA</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K42" s="0">
+        <v>2800</v>
+      </c>
+      <c r="L42" s="0">
         <v>2</v>
       </c>
-      <c r="N34" s="0">
+      <c r="N42" s="0">
+        <v>5600</v>
+      </c>
+      <c r="O42" s="0">
+        <v>5600</v>
+      </c>
+      <c r="P42" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q42" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R42" s="0" t="inlineStr">
+        <is>
+          <t>S5596 Edit S5596Clone</t>
+        </is>
+      </c>
+      <c r="S42" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:51 pm</t>
+        </is>
+      </c>
+      <c r="T42" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U42" s="0">
+        <v>3</v>
+      </c>
+      <c r="V42" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W42" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Walk-in Customers </t>
+        </is>
+      </c>
+      <c r="Z42" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>10500</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>10500</v>
+      </c>
+      <c r="AC42" s="0" t="inlineStr">
+        <is>
+          <t>Cash: ₦10,500.00</t>
+        </is>
+      </c>
+      <c r="AD42" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:31">
+      <c r="A43" s="0">
+        <v>131</v>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>DISCO WAX</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K43" s="0">
+        <v>10500</v>
+      </c>
+      <c r="L43" s="0">
+        <v>2</v>
+      </c>
+      <c r="N43" s="0">
+        <v>21000</v>
+      </c>
+      <c r="O43" s="0">
+        <v>21000</v>
+      </c>
+      <c r="P43" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q43" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R43" s="0" t="inlineStr">
+        <is>
+          <t>S5597 Edit S5597Clone</t>
+        </is>
+      </c>
+      <c r="S43" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:52 pm</t>
+        </is>
+      </c>
+      <c r="T43" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U43" s="0">
+        <v>2</v>
+      </c>
+      <c r="V43" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W43" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Walk-in Customers </t>
+        </is>
+      </c>
+      <c r="Z43" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>21000</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>21000</v>
+      </c>
+      <c r="AC43" s="0" t="inlineStr">
+        <is>
+          <t>Cash: ₦1,000.00MONIEPOINT: ₦20,000.00</t>
+        </is>
+      </c>
+      <c r="AD43" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:31">
+      <c r="A44" s="0">
+        <v>104</v>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY COTTON POPLIN</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K44" s="0">
+        <v>26000</v>
+      </c>
+      <c r="L44" s="0">
+        <v>1</v>
+      </c>
+      <c r="N44" s="0">
+        <v>26000</v>
+      </c>
+      <c r="O44" s="0">
+        <v>26000</v>
+      </c>
+      <c r="P44" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q44" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R44" s="0" t="inlineStr">
+        <is>
+          <t>S5598 Edit S5598Clone</t>
+        </is>
+      </c>
+      <c r="S44" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:52 pm</t>
+        </is>
+      </c>
+      <c r="T44" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U44" s="0">
+        <v>2</v>
+      </c>
+      <c r="V44" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W44" s="0" t="inlineStr">
+        <is>
+          <t>Shamsu Shop </t>
+        </is>
+      </c>
+      <c r="Z44" s="0">
+        <v>27</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>45000</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>45000</v>
+      </c>
+      <c r="AC44" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦46,000.00Cash: -₦1,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:31">
+      <c r="A45" s="0">
+        <v>111</v>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>FULL STONE EMBELLISHED </t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K45" s="0">
+        <v>19000</v>
+      </c>
+      <c r="L45" s="0">
+        <v>1</v>
+      </c>
+      <c r="N45" s="0">
+        <v>19000</v>
+      </c>
+      <c r="O45" s="0">
+        <v>19000</v>
+      </c>
+      <c r="P45" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q45" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R45" s="0" t="inlineStr">
+        <is>
+          <t>S5598 Edit S5598Clone</t>
+        </is>
+      </c>
+      <c r="S45" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:52 pm</t>
+        </is>
+      </c>
+      <c r="T45" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U45" s="0">
+        <v>2</v>
+      </c>
+      <c r="V45" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W45" s="0" t="inlineStr">
+        <is>
+          <t>Shamsu Shop </t>
+        </is>
+      </c>
+      <c r="Z45" s="0">
+        <v>27</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>45000</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>45000</v>
+      </c>
+      <c r="AC45" s="0" t="inlineStr">
+        <is>
+          <t>MONIEPOINT: ₦46,000.00Cash: -₦1,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:31">
+      <c r="A46" s="0">
+        <v>143</v>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>ROBA ATAMPA</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K46" s="0">
+        <v>2800</v>
+      </c>
+      <c r="L46" s="0">
+        <v>3</v>
+      </c>
+      <c r="N46" s="0">
+        <v>8400</v>
+      </c>
+      <c r="O46" s="0">
+        <v>8400</v>
+      </c>
+      <c r="P46" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q46" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R46" s="0" t="inlineStr">
+        <is>
+          <t>S5599 Edit S5599Clone</t>
+        </is>
+      </c>
+      <c r="S46" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:56 pm</t>
+        </is>
+      </c>
+      <c r="T46" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U46" s="0">
+        <v>3</v>
+      </c>
+      <c r="V46" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W46" s="0" t="inlineStr">
+        <is>
+          <t>Tahir Walk-in Customers </t>
+        </is>
+      </c>
+      <c r="Z46" s="0">
+        <v>23</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>8400</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>8400</v>
+      </c>
+      <c r="AC46" s="0" t="inlineStr">
+        <is>
+          <t>Cash: ₦8,400.00</t>
+        </is>
+      </c>
+      <c r="AD46" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:31">
+      <c r="A47" s="0">
+        <v>138</v>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>HOLLANDAD</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K47" s="0">
+        <v>8300</v>
+      </c>
+      <c r="L47" s="0">
+        <v>1</v>
+      </c>
+      <c r="N47" s="0">
+        <v>8300</v>
+      </c>
+      <c r="O47" s="0">
+        <v>8300</v>
+      </c>
+      <c r="P47" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q47" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R47" s="0" t="inlineStr">
+        <is>
+          <t>S5600 Edit S5600Clone</t>
+        </is>
+      </c>
+      <c r="S47" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:57 pm</t>
+        </is>
+      </c>
+      <c r="T47" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U47" s="0">
+        <v>1</v>
+      </c>
+      <c r="V47" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W47" s="0" t="inlineStr">
+        <is>
+          <t>Khalid Abasu Kala  </t>
+        </is>
+      </c>
+      <c r="Z47" s="0">
+        <v>51</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>8300</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>8300</v>
+      </c>
+      <c r="AC47" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦8,300.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:31">
+      <c r="A48" s="0">
+        <v>86</v>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>LATEST ULTRA EMBELLISHED </t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K48" s="0">
         <v>38000</v>
       </c>
-      <c r="O34" s="0">
+      <c r="L48" s="0">
+        <v>1</v>
+      </c>
+      <c r="N48" s="0">
         <v>38000</v>
       </c>
-      <c r="P34" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q34" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R34" s="0" t="inlineStr">
-        <is>
-          <t>S5164 Edit S5164Clone</t>
-        </is>
-      </c>
-      <c r="S34" s="0" t="inlineStr">
-        <is>
-          <t>08/26/2026-06:21 pm</t>
-        </is>
-      </c>
-      <c r="T34" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U34" s="0">
+      <c r="O48" s="0">
+        <v>38000</v>
+      </c>
+      <c r="P48" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q48" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R48" s="0" t="inlineStr">
+        <is>
+          <t>S5601 Edit S5601Clone</t>
+        </is>
+      </c>
+      <c r="S48" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:57 pm</t>
+        </is>
+      </c>
+      <c r="T48" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U48" s="0">
+        <v>1</v>
+      </c>
+      <c r="V48" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W48" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z48" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>38000</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>38000</v>
+      </c>
+      <c r="AC48" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦38,000.00</t>
+        </is>
+      </c>
+      <c r="AD48" s="0" t="inlineStr">
+        <is>
+          <t>AUWAL FMK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:31">
+      <c r="A49" s="0">
+        <v>196</v>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>Fantastic Holland</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI (3)</t>
+        </is>
+      </c>
+      <c r="K49" s="0">
+        <v>8500</v>
+      </c>
+      <c r="L49" s="0">
+        <v>1</v>
+      </c>
+      <c r="N49" s="0">
+        <v>8500</v>
+      </c>
+      <c r="O49" s="0">
+        <v>8500</v>
+      </c>
+      <c r="P49" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q49" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R49" s="0" t="inlineStr">
+        <is>
+          <t>S5602 Edit S5602Clone</t>
+        </is>
+      </c>
+      <c r="S49" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:58 pm</t>
+        </is>
+      </c>
+      <c r="T49" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U49" s="0">
+        <v>1</v>
+      </c>
+      <c r="V49" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W49" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z49" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA49" s="0">
+        <v>8500</v>
+      </c>
+      <c r="AB49" s="0">
+        <v>8500</v>
+      </c>
+      <c r="AC49" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦8,500.00</t>
+        </is>
+      </c>
+      <c r="AD49" s="0" t="inlineStr">
+        <is>
+          <t>HAJ HAFSAT SAIDU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:31">
+      <c r="A50" s="0">
+        <v>48</v>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>FLORA MATERIAL </t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K50" s="0">
+        <v>16000</v>
+      </c>
+      <c r="L50" s="0">
+        <v>1</v>
+      </c>
+      <c r="N50" s="0">
+        <v>16000</v>
+      </c>
+      <c r="O50" s="0">
+        <v>16000</v>
+      </c>
+      <c r="P50" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q50" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R50" s="0" t="inlineStr">
+        <is>
+          <t>S5603 Edit S5603Clone</t>
+        </is>
+      </c>
+      <c r="S50" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:58 pm</t>
+        </is>
+      </c>
+      <c r="T50" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U50" s="0">
         <v>2</v>
       </c>
-      <c r="V34" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W34" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z34" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA34" s="0">
-        <v>38000</v>
-      </c>
-      <c r="AB34" s="0">
-        <v>38000</v>
-      </c>
-      <c r="AC34" s="0" t="inlineStr">
-        <is>
-          <t>MONIEPOINT: ₦38,000.00</t>
-        </is>
-      </c>
-      <c r="AD34" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+      <c r="V50" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W50" s="0" t="inlineStr">
+        <is>
+          <t>AISHA JARMA</t>
+        </is>
+      </c>
+      <c r="Z50" s="0">
+        <v>274</v>
+      </c>
+      <c r="AA50" s="0">
+        <v>30000</v>
+      </c>
+      <c r="AB50" s="0">
+        <v>30000</v>
+      </c>
+      <c r="AC50" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦30,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:31">
+      <c r="A51" s="0">
+        <v>215</v>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>Baby Blueberry Material</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K51" s="0">
+        <v>14000</v>
+      </c>
+      <c r="L51" s="0">
+        <v>1</v>
+      </c>
+      <c r="N51" s="0">
+        <v>14000</v>
+      </c>
+      <c r="O51" s="0">
+        <v>14000</v>
+      </c>
+      <c r="P51" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q51" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R51" s="0" t="inlineStr">
+        <is>
+          <t>S5603 Edit S5603Clone</t>
+        </is>
+      </c>
+      <c r="S51" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:58 pm</t>
+        </is>
+      </c>
+      <c r="T51" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U51" s="0">
+        <v>2</v>
+      </c>
+      <c r="V51" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W51" s="0" t="inlineStr">
+        <is>
+          <t>AISHA JARMA</t>
+        </is>
+      </c>
+      <c r="Z51" s="0">
+        <v>274</v>
+      </c>
+      <c r="AA51" s="0">
+        <v>30000</v>
+      </c>
+      <c r="AB51" s="0">
+        <v>30000</v>
+      </c>
+      <c r="AC51" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦30,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:31">
+      <c r="A52" s="0">
+        <v>187</v>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>TYCOON AND GAZA WOOL</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>YARD</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K52" s="0">
+        <v>4500</v>
+      </c>
+      <c r="L52" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="N52" s="0">
+        <v>15750</v>
+      </c>
+      <c r="O52" s="0">
+        <v>15750</v>
+      </c>
+      <c r="P52" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q52" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R52" s="0" t="inlineStr">
+        <is>
+          <t>S5604 Edit S5604Clone</t>
+        </is>
+      </c>
+      <c r="S52" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-05:59 pm</t>
+        </is>
+      </c>
+      <c r="T52" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U52" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="V52" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W52" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir Shop </t>
+        </is>
+      </c>
+      <c r="Z52" s="0">
+        <v>24</v>
+      </c>
+      <c r="AA52" s="0">
+        <v>15750</v>
+      </c>
+      <c r="AB52" s="0">
+        <v>15750</v>
+      </c>
+      <c r="AC52" s="0" t="inlineStr">
+        <is>
+          <t>ACCESS BANK: ₦15,750.00</t>
+        </is>
+      </c>
+      <c r="AD52" s="0" t="inlineStr">
+        <is>
+          <t>DALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:31">
+      <c r="A53" s="0">
+        <v>104</v>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>CHIGANVY COTTON POPLIN</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K53" s="0">
+        <v>26000</v>
+      </c>
+      <c r="L53" s="0">
+        <v>1</v>
+      </c>
+      <c r="N53" s="0">
+        <v>26000</v>
+      </c>
+      <c r="O53" s="0">
+        <v>26000</v>
+      </c>
+      <c r="P53" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q53" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R53" s="0" t="inlineStr">
+        <is>
+          <t>S5605 Edit S5605Clone</t>
+        </is>
+      </c>
+      <c r="S53" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-06:00 pm</t>
+        </is>
+      </c>
+      <c r="T53" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U53" s="0">
+        <v>2</v>
+      </c>
+      <c r="V53" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W53" s="0" t="inlineStr">
+        <is>
+          <t>Haj Hadiza Pretty </t>
+        </is>
+      </c>
+      <c r="Z53" s="0">
+        <v>34</v>
+      </c>
+      <c r="AA53" s="0">
+        <v>43000</v>
+      </c>
+      <c r="AB53" s="0">
+        <v>43000</v>
+      </c>
+      <c r="AC53" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦43,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="1:31">
+      <c r="A54" s="0">
+        <v>117</v>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>EMBELLISHED MDT</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t> ()</t>
+        </is>
+      </c>
+      <c r="K54" s="0">
+        <v>17000</v>
+      </c>
+      <c r="L54" s="0">
+        <v>1</v>
+      </c>
+      <c r="N54" s="0">
+        <v>17000</v>
+      </c>
+      <c r="O54" s="0">
+        <v>17000</v>
+      </c>
+      <c r="P54" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q54" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R54" s="0" t="inlineStr">
+        <is>
+          <t>S5605 Edit S5605Clone</t>
+        </is>
+      </c>
+      <c r="S54" s="0" t="inlineStr">
+        <is>
+          <t>09/07/2026-06:00 pm</t>
+        </is>
+      </c>
+      <c r="T54" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U54" s="0">
+        <v>2</v>
+      </c>
+      <c r="V54" s="0" t="inlineStr">
+        <is>
+          <t>BB </t>
+        </is>
+      </c>
+      <c r="W54" s="0" t="inlineStr">
+        <is>
+          <t>Haj Hadiza Pretty </t>
+        </is>
+      </c>
+      <c r="Z54" s="0">
+        <v>34</v>
+      </c>
+      <c r="AA54" s="0">
+        <v>43000</v>
+      </c>
+      <c r="AB54" s="0">
+        <v>43000</v>
+      </c>
+      <c r="AC54" s="0" t="inlineStr">
+        <is>
+          <t>Store Account: ₦43,000.00</t>
         </is>
       </c>
     </row>

--- a/Excels/DSR.xlsx
+++ b/Excels/DSR.xlsx
@@ -211,11 +211,11 @@
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="0">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>CHIGANVY INDIA</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -229,16 +229,16 @@
         </is>
       </c>
       <c r="K2" s="0">
-        <v>15500</v>
+        <v>8000</v>
       </c>
       <c r="L2" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" s="0">
-        <v>31000</v>
+        <v>8000</v>
       </c>
       <c r="O2" s="0">
-        <v>31000</v>
+        <v>8000</v>
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
@@ -252,12 +252,12 @@
       </c>
       <c r="R2" s="0" t="inlineStr">
         <is>
-          <t>S6092 Edit S6092Clone</t>
+          <t>S6314 Edit S6314Clone</t>
         </is>
       </c>
       <c r="S2" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-12:05 pm</t>
+          <t>09/29/2026-12:50 pm</t>
         </is>
       </c>
       <c r="T2" s="0" t="inlineStr">
@@ -266,45 +266,45 @@
         </is>
       </c>
       <c r="U2" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V2" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W2" s="0" t="inlineStr">
         <is>
-          <t>TAHIR ONLINE SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z2" s="0">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AA2" s="0">
-        <v>59500</v>
+        <v>8000</v>
       </c>
       <c r="AB2" s="0">
-        <v>59500</v>
+        <v>8000</v>
       </c>
       <c r="AC2" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦59,500.00</t>
+          <t>MONIEPOINT: ₦8,000.00</t>
         </is>
       </c>
       <c r="AD2" s="0" t="inlineStr">
         <is>
-          <t>Auwalu online </t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:31">
       <c r="A3" s="0">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>SUPER FAMOUS</t>
+          <t>Hollantex Mix pattern</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -318,16 +318,16 @@
         </is>
       </c>
       <c r="K3" s="0">
-        <v>9500</v>
+        <v>15000</v>
       </c>
       <c r="L3" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N3" s="0">
-        <v>28500</v>
+        <v>15000</v>
       </c>
       <c r="O3" s="0">
-        <v>28500</v>
+        <v>15000</v>
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
@@ -341,12 +341,12 @@
       </c>
       <c r="R3" s="0" t="inlineStr">
         <is>
-          <t>S6092 Edit S6092Clone</t>
+          <t>S6315 Edit S6315Clone</t>
         </is>
       </c>
       <c r="S3" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-12:05 pm</t>
+          <t>09/29/2026-01:49 pm</t>
         </is>
       </c>
       <c r="T3" s="0" t="inlineStr">
@@ -355,45 +355,45 @@
         </is>
       </c>
       <c r="U3" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W3" s="0" t="inlineStr">
         <is>
-          <t>TAHIR ONLINE SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z3" s="0">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="0">
-        <v>59500</v>
+        <v>15000</v>
       </c>
       <c r="AB3" s="0">
-        <v>59500</v>
+        <v>15000</v>
       </c>
       <c r="AC3" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦59,500.00</t>
+          <t>MONIEPOINT: ₦15,000.00</t>
         </is>
       </c>
       <c r="AD3" s="0" t="inlineStr">
         <is>
-          <t>Auwalu online </t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:31">
       <c r="A4" s="0">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>NEW JULIUS HOLLAND</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -407,16 +407,16 @@
         </is>
       </c>
       <c r="K4" s="0">
-        <v>17000</v>
+        <v>68000</v>
       </c>
       <c r="L4" s="0">
         <v>2</v>
       </c>
       <c r="N4" s="0">
-        <v>34000</v>
+        <v>136000</v>
       </c>
       <c r="O4" s="0">
-        <v>34000</v>
+        <v>136000</v>
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
@@ -430,12 +430,12 @@
       </c>
       <c r="R4" s="0" t="inlineStr">
         <is>
-          <t>S6093 Edit S6093Clone</t>
+          <t>S6316 Edit S6316Clone</t>
         </is>
       </c>
       <c r="S4" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-12:47 pm</t>
+          <t>09/29/2026-02:23 pm</t>
         </is>
       </c>
       <c r="T4" s="0" t="inlineStr">
@@ -460,14 +460,14 @@
         <v>23</v>
       </c>
       <c r="AA4" s="0">
-        <v>34000</v>
+        <v>136000</v>
       </c>
       <c r="AB4" s="0">
-        <v>34000</v>
+        <v>136000</v>
       </c>
       <c r="AC4" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦34,000.00</t>
+          <t>MONIEPOINT: ₦136,000.00</t>
         </is>
       </c>
       <c r="AD4" s="0" t="inlineStr">
@@ -478,11 +478,11 @@
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="0">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>GLITTER ROBA </t>
+          <t>Rotana holland</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -492,20 +492,20 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>YAYA SANI (3)</t>
         </is>
       </c>
       <c r="K5" s="0">
-        <v>5200</v>
+        <v>8500</v>
       </c>
       <c r="L5" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N5" s="0">
-        <v>104000</v>
+        <v>42500</v>
       </c>
       <c r="O5" s="0">
-        <v>104000</v>
+        <v>42500</v>
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
@@ -519,12 +519,12 @@
       </c>
       <c r="R5" s="0" t="inlineStr">
         <is>
-          <t>S6094 Edit S6094Clone</t>
+          <t>S6317 Edit S6317Clone</t>
         </is>
       </c>
       <c r="S5" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-02:51 pm</t>
+          <t>09/29/2026-02:28 pm</t>
         </is>
       </c>
       <c r="T5" s="0" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="U5" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
@@ -542,21 +542,21 @@
       </c>
       <c r="W5" s="0" t="inlineStr">
         <is>
-          <t>Shamsu Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z5" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA5" s="0">
-        <v>133000</v>
+        <v>42500</v>
       </c>
       <c r="AB5" s="0">
-        <v>133000</v>
+        <v>42500</v>
       </c>
       <c r="AC5" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦133,000.00</t>
+          <t>MONIEPOINT: ₦42,500.00</t>
         </is>
       </c>
       <c r="AD5" s="0" t="inlineStr">
@@ -567,11 +567,11 @@
     </row>
     <row r="6" spans="1:31">
       <c r="A6" s="0">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>CHIGANVY COTTON POPLIN</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -581,20 +581,20 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K6" s="0">
-        <v>14500</v>
+        <v>27000</v>
       </c>
       <c r="L6" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="0">
-        <v>29000</v>
+        <v>27000</v>
       </c>
       <c r="O6" s="0">
-        <v>29000</v>
+        <v>27000</v>
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
@@ -608,12 +608,12 @@
       </c>
       <c r="R6" s="0" t="inlineStr">
         <is>
-          <t>S6094 Edit S6094Clone</t>
+          <t>S6318 Edit S6318Clone</t>
         </is>
       </c>
       <c r="S6" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-02:51 pm</t>
+          <t>09/29/2026-02:43 pm</t>
         </is>
       </c>
       <c r="T6" s="0" t="inlineStr">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="U6" s="0">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="V6" s="0" t="inlineStr">
         <is>
@@ -631,21 +631,21 @@
       </c>
       <c r="W6" s="0" t="inlineStr">
         <is>
-          <t>Shamsu Shop </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z6" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA6" s="0">
-        <v>133000</v>
+        <v>109000</v>
       </c>
       <c r="AB6" s="0">
-        <v>133000</v>
+        <v>109000</v>
       </c>
       <c r="AC6" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦133,000.00</t>
+          <t>Cash: ₦109,000.00</t>
         </is>
       </c>
       <c r="AD6" s="0" t="inlineStr">
@@ -656,11 +656,11 @@
     </row>
     <row r="7" spans="1:31">
       <c r="A7" s="0">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
+          <t>Luxe Embellished MD</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K7" s="0">
-        <v>260000</v>
+        <v>17000</v>
       </c>
       <c r="L7" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" s="0">
-        <v>780000</v>
+        <v>34000</v>
       </c>
       <c r="O7" s="0">
-        <v>780000</v>
+        <v>34000</v>
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
@@ -697,12 +697,12 @@
       </c>
       <c r="R7" s="0" t="inlineStr">
         <is>
-          <t>S6095 Edit S6095Clone</t>
+          <t>S6318 Edit S6318Clone</t>
         </is>
       </c>
       <c r="S7" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-03:23 pm</t>
+          <t>09/29/2026-02:43 pm</t>
         </is>
       </c>
       <c r="T7" s="0" t="inlineStr">
@@ -711,40 +711,45 @@
         </is>
       </c>
       <c r="U7" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W7" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z7" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AA7" s="0">
-        <v>1150000</v>
+        <v>109000</v>
       </c>
       <c r="AB7" s="0">
-        <v>1150000</v>
+        <v>109000</v>
       </c>
       <c r="AC7" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦1,150,000.00</t>
+          <t>Cash: ₦109,000.00</t>
+        </is>
+      </c>
+      <c r="AD7" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="0">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND WAX</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -758,16 +763,16 @@
         </is>
       </c>
       <c r="K8" s="0">
-        <v>185000</v>
+        <v>16000</v>
       </c>
       <c r="L8" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" s="0">
-        <v>370000</v>
+        <v>48000</v>
       </c>
       <c r="O8" s="0">
-        <v>370000</v>
+        <v>48000</v>
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
@@ -781,12 +786,12 @@
       </c>
       <c r="R8" s="0" t="inlineStr">
         <is>
-          <t>S6095 Edit S6095Clone</t>
+          <t>S6318 Edit S6318Clone</t>
         </is>
       </c>
       <c r="S8" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-03:23 pm</t>
+          <t>09/29/2026-02:43 pm</t>
         </is>
       </c>
       <c r="T8" s="0" t="inlineStr">
@@ -795,40 +800,45 @@
         </is>
       </c>
       <c r="U8" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z8" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AA8" s="0">
-        <v>1150000</v>
+        <v>109000</v>
       </c>
       <c r="AB8" s="0">
-        <v>1150000</v>
+        <v>109000</v>
       </c>
       <c r="AC8" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦1,150,000.00</t>
+          <t>Cash: ₦109,000.00</t>
+        </is>
+      </c>
+      <c r="AD8" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="0">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>MEDIUM GLITTER</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -842,16 +852,16 @@
         </is>
       </c>
       <c r="K9" s="0">
-        <v>14000</v>
+        <v>17500</v>
       </c>
       <c r="L9" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" s="0">
-        <v>42000</v>
+        <v>17500</v>
       </c>
       <c r="O9" s="0">
-        <v>42000</v>
+        <v>17500</v>
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
@@ -865,12 +875,12 @@
       </c>
       <c r="R9" s="0" t="inlineStr">
         <is>
-          <t>S6096 Edit S6096Clone</t>
+          <t>S6319 Edit S6319Clone</t>
         </is>
       </c>
       <c r="S9" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-03:29 pm</t>
+          <t>09/29/2026-02:46 pm</t>
         </is>
       </c>
       <c r="T9" s="0" t="inlineStr">
@@ -879,7 +889,7 @@
         </is>
       </c>
       <c r="U9" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V9" s="0" t="inlineStr">
         <is>
@@ -895,14 +905,14 @@
         <v>23</v>
       </c>
       <c r="AA9" s="0">
-        <v>42000</v>
+        <v>17500</v>
       </c>
       <c r="AB9" s="0">
-        <v>42000</v>
+        <v>17500</v>
       </c>
       <c r="AC9" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦42,000.00</t>
+          <t>MONIEPOINT: ₦17,500.00</t>
         </is>
       </c>
       <c r="AD9" s="0" t="inlineStr">
@@ -913,16 +923,16 @@
     </row>
     <row r="10" spans="1:31">
       <c r="A10" s="0">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>BELLDAM</t>
+          <t>SWISS LACE B</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
@@ -931,16 +941,16 @@
         </is>
       </c>
       <c r="K10" s="0">
-        <v>5000</v>
+        <v>82000</v>
       </c>
       <c r="L10" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N10" s="0">
-        <v>30000</v>
+        <v>82000</v>
       </c>
       <c r="O10" s="0">
-        <v>30000</v>
+        <v>82000</v>
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
@@ -954,12 +964,12 @@
       </c>
       <c r="R10" s="0" t="inlineStr">
         <is>
-          <t>S6097 Edit S6097Clone</t>
+          <t>S6320 Edit S6320Clone</t>
         </is>
       </c>
       <c r="S10" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-03:41 pm</t>
+          <t>09/29/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T10" s="0" t="inlineStr">
@@ -968,7 +978,7 @@
         </is>
       </c>
       <c r="U10" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V10" s="0" t="inlineStr">
         <is>
@@ -984,14 +994,14 @@
         <v>23</v>
       </c>
       <c r="AA10" s="0">
-        <v>30000</v>
+        <v>328000</v>
       </c>
       <c r="AB10" s="0">
-        <v>30000</v>
+        <v>328000</v>
       </c>
       <c r="AC10" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦30,000.00</t>
+          <t>MONIEPOINT: ₦328,000.00</t>
         </is>
       </c>
       <c r="AD10" s="0" t="inlineStr">
@@ -1002,34 +1012,34 @@
     </row>
     <row r="11" spans="1:31">
       <c r="A11" s="0">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>Fantastic Holland</t>
+          <t>SWISS LACE D</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>YAYA SANI (3)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K11" s="0">
-        <v>8300</v>
+        <v>60000</v>
       </c>
       <c r="L11" s="0">
         <v>1</v>
       </c>
       <c r="N11" s="0">
-        <v>8300</v>
+        <v>60000</v>
       </c>
       <c r="O11" s="0">
-        <v>8300</v>
+        <v>60000</v>
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
@@ -1043,12 +1053,12 @@
       </c>
       <c r="R11" s="0" t="inlineStr">
         <is>
-          <t>S6098 Edit S6098Clone</t>
+          <t>S6320 Edit S6320Clone</t>
         </is>
       </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-03:42 pm</t>
+          <t>09/29/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T11" s="0" t="inlineStr">
@@ -1057,7 +1067,7 @@
         </is>
       </c>
       <c r="U11" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V11" s="0" t="inlineStr">
         <is>
@@ -1073,34 +1083,34 @@
         <v>23</v>
       </c>
       <c r="AA11" s="0">
-        <v>8300</v>
+        <v>328000</v>
       </c>
       <c r="AB11" s="0">
-        <v>8300</v>
+        <v>328000</v>
       </c>
       <c r="AC11" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦8,300.00</t>
+          <t>MONIEPOINT: ₦328,000.00</t>
         </is>
       </c>
       <c r="AD11" s="0" t="inlineStr">
         <is>
-          <t>JAZULI</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:31">
       <c r="A12" s="0">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND EMBELLISHED</t>
+          <t>SWISS LAFAYA A</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
@@ -1109,16 +1119,16 @@
         </is>
       </c>
       <c r="K12" s="0">
-        <v>240000</v>
+        <v>57000</v>
       </c>
       <c r="L12" s="0">
         <v>1</v>
       </c>
       <c r="N12" s="0">
-        <v>240000</v>
+        <v>57000</v>
       </c>
       <c r="O12" s="0">
-        <v>240000</v>
+        <v>57000</v>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
@@ -1132,12 +1142,12 @@
       </c>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t>S6099 Edit S6099Clone</t>
+          <t>S6320 Edit S6320Clone</t>
         </is>
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:03 pm</t>
+          <t>09/29/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T12" s="0" t="inlineStr">
@@ -1146,45 +1156,45 @@
         </is>
       </c>
       <c r="U12" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V12" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W12" s="0" t="inlineStr">
         <is>
-          <t>TAHIR ONLINE SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z12" s="0">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AA12" s="0">
-        <v>486600</v>
+        <v>328000</v>
       </c>
       <c r="AB12" s="0">
-        <v>486600</v>
+        <v>328000</v>
       </c>
       <c r="AC12" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦486,600.00</t>
+          <t>MONIEPOINT: ₦328,000.00</t>
         </is>
       </c>
       <c r="AD12" s="0" t="inlineStr">
         <is>
-          <t>Auwalu online</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:31">
       <c r="A13" s="0">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND EMBELLISHED</t>
+          <t>CHIGANVY COTTON POPLIN</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -1198,16 +1208,16 @@
         </is>
       </c>
       <c r="K13" s="0">
-        <v>230000</v>
+        <v>27000</v>
       </c>
       <c r="L13" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="0">
-        <v>230000</v>
+        <v>54000</v>
       </c>
       <c r="O13" s="0">
-        <v>230000</v>
+        <v>54000</v>
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
@@ -1221,12 +1231,12 @@
       </c>
       <c r="R13" s="0" t="inlineStr">
         <is>
-          <t>S6099 Edit S6099Clone</t>
+          <t>S6320 Edit S6320Clone</t>
         </is>
       </c>
       <c r="S13" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:03 pm</t>
+          <t>09/29/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T13" s="0" t="inlineStr">
@@ -1235,68 +1245,68 @@
         </is>
       </c>
       <c r="U13" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V13" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
-          <t>TAHIR ONLINE SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z13" s="0">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AA13" s="0">
-        <v>486600</v>
+        <v>328000</v>
       </c>
       <c r="AB13" s="0">
-        <v>486600</v>
+        <v>328000</v>
       </c>
       <c r="AC13" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦486,600.00</t>
+          <t>MONIEPOINT: ₦328,000.00</t>
         </is>
       </c>
       <c r="AD13" s="0" t="inlineStr">
         <is>
-          <t>Auwalu online</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:31">
       <c r="A14" s="0">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>Fantastic Holland</t>
+          <t>LAGOS LACE C</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>YAYA SANI (3)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K14" s="0">
-        <v>8300</v>
+        <v>25000</v>
       </c>
       <c r="L14" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="0">
-        <v>16600</v>
+        <v>75000</v>
       </c>
       <c r="O14" s="0">
-        <v>16600</v>
+        <v>75000</v>
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
@@ -1310,12 +1320,12 @@
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t>S6099 Edit S6099Clone</t>
+          <t>S6320 Edit S6320Clone</t>
         </is>
       </c>
       <c r="S14" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:03 pm</t>
+          <t>09/29/2026-05:29 pm</t>
         </is>
       </c>
       <c r="T14" s="0" t="inlineStr">
@@ -1324,45 +1334,45 @@
         </is>
       </c>
       <c r="U14" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V14" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
-          <t>TAHIR ONLINE SHOP </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z14" s="0">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AA14" s="0">
-        <v>486600</v>
+        <v>328000</v>
       </c>
       <c r="AB14" s="0">
-        <v>486600</v>
+        <v>328000</v>
       </c>
       <c r="AC14" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦486,600.00</t>
+          <t>MONIEPOINT: ₦328,000.00</t>
         </is>
       </c>
       <c r="AD14" s="0" t="inlineStr">
         <is>
-          <t>Auwalu online</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:31">
       <c r="A15" s="0">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -1376,16 +1386,16 @@
         </is>
       </c>
       <c r="K15" s="0">
-        <v>16500</v>
+        <v>16000</v>
       </c>
       <c r="L15" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N15" s="0">
-        <v>66000</v>
+        <v>16000</v>
       </c>
       <c r="O15" s="0">
-        <v>66000</v>
+        <v>16000</v>
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
@@ -1399,12 +1409,12 @@
       </c>
       <c r="R15" s="0" t="inlineStr">
         <is>
-          <t>S6100 Edit S6100Clone</t>
+          <t>S6321 Edit S6321Clone</t>
         </is>
       </c>
       <c r="S15" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:09 pm</t>
+          <t>09/29/2026-05:41 pm</t>
         </is>
       </c>
       <c r="T15" s="0" t="inlineStr">
@@ -1413,45 +1423,40 @@
         </is>
       </c>
       <c r="U15" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V15" s="0" t="inlineStr">
         <is>
-          <t>ABBA  </t>
+          <t>BB </t>
         </is>
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
-          <t>TAHIR ONLINE SHOP </t>
+          <t>Jamila Baba </t>
         </is>
       </c>
       <c r="Z15" s="0">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="AA15" s="0">
-        <v>66000</v>
+        <v>16000</v>
       </c>
       <c r="AB15" s="0">
-        <v>66000</v>
+        <v>16000</v>
       </c>
       <c r="AC15" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦66,000.00</t>
-        </is>
-      </c>
-      <c r="AD15" s="0" t="inlineStr">
-        <is>
-          <t>Ibrahim online</t>
+          <t>Store Account: ₦16,000.00</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:31">
       <c r="A16" s="0">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM GLITTER</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -1465,16 +1470,16 @@
         </is>
       </c>
       <c r="K16" s="0">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="L16" s="0">
         <v>2</v>
       </c>
       <c r="N16" s="0">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="O16" s="0">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="P16" s="0" t="inlineStr">
         <is>
@@ -1488,12 +1493,12 @@
       </c>
       <c r="R16" s="0" t="inlineStr">
         <is>
-          <t>S6101 Edit S6101Clone</t>
+          <t>S6322 Edit S6322Clone</t>
         </is>
       </c>
       <c r="S16" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:15 pm</t>
+          <t>09/29/2026-05:41 pm</t>
         </is>
       </c>
       <c r="T16" s="0" t="inlineStr">
@@ -1502,7 +1507,7 @@
         </is>
       </c>
       <c r="U16" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V16" s="0" t="inlineStr">
         <is>
@@ -1511,36 +1516,31 @@
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>HAJ BILKISU </t>
         </is>
       </c>
       <c r="Z16" s="0">
-        <v>23</v>
+        <v>220</v>
       </c>
       <c r="AA16" s="0">
-        <v>138500</v>
+        <v>32000</v>
       </c>
       <c r="AB16" s="0">
-        <v>138500</v>
+        <v>32000</v>
       </c>
       <c r="AC16" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦138,500.00</t>
-        </is>
-      </c>
-      <c r="AD16" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦32,000.00</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:31">
       <c r="A17" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="K17" s="0">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="L17" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="0">
-        <v>17000</v>
+        <v>32000</v>
       </c>
       <c r="O17" s="0">
-        <v>17000</v>
+        <v>32000</v>
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="R17" s="0" t="inlineStr">
         <is>
-          <t>S6101 Edit S6101Clone</t>
+          <t>S6323 Edit S6323Clone</t>
         </is>
       </c>
       <c r="S17" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:15 pm</t>
+          <t>09/29/2026-05:42 pm</t>
         </is>
       </c>
       <c r="T17" s="0" t="inlineStr">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="U17" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V17" s="0" t="inlineStr">
         <is>
@@ -1600,36 +1600,31 @@
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>HAJ MAIMUNA AGAJI</t>
         </is>
       </c>
       <c r="Z17" s="0">
-        <v>23</v>
+        <v>368</v>
       </c>
       <c r="AA17" s="0">
-        <v>138500</v>
+        <v>32000</v>
       </c>
       <c r="AB17" s="0">
-        <v>138500</v>
+        <v>32000</v>
       </c>
       <c r="AC17" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦138,500.00</t>
-        </is>
-      </c>
-      <c r="AD17" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦32,000.00</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:31">
       <c r="A18" s="0">
-        <v>118</v>
+        <v>220</v>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>PRESTIGE EMBELLISHED</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -1643,16 +1638,16 @@
         </is>
       </c>
       <c r="K18" s="0">
-        <v>17500</v>
+        <v>16000</v>
       </c>
       <c r="L18" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N18" s="0">
-        <v>17500</v>
+        <v>48000</v>
       </c>
       <c r="O18" s="0">
-        <v>17500</v>
+        <v>48000</v>
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
@@ -1666,12 +1661,12 @@
       </c>
       <c r="R18" s="0" t="inlineStr">
         <is>
-          <t>S6101 Edit S6101Clone</t>
+          <t>S6324 Edit S6324Clone</t>
         </is>
       </c>
       <c r="S18" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:15 pm</t>
+          <t>09/29/2026-05:42 pm</t>
         </is>
       </c>
       <c r="T18" s="0" t="inlineStr">
@@ -1680,7 +1675,7 @@
         </is>
       </c>
       <c r="U18" s="0">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="V18" s="0" t="inlineStr">
         <is>
@@ -1689,36 +1684,31 @@
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>RUKAYYA WADA </t>
         </is>
       </c>
       <c r="Z18" s="0">
-        <v>23</v>
+        <v>369</v>
       </c>
       <c r="AA18" s="0">
-        <v>138500</v>
+        <v>48000</v>
       </c>
       <c r="AB18" s="0">
-        <v>138500</v>
+        <v>48000</v>
       </c>
       <c r="AC18" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦138,500.00</t>
-        </is>
-      </c>
-      <c r="AD18" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦48,000.00</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:31">
       <c r="A19" s="0">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>HOLLANDAD</t>
+          <t>CHIGANVY COTONOU PLAIN</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -1732,16 +1722,16 @@
         </is>
       </c>
       <c r="K19" s="0">
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="L19" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="0">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="O19" s="0">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="P19" s="0" t="inlineStr">
         <is>
@@ -1755,12 +1745,12 @@
       </c>
       <c r="R19" s="0" t="inlineStr">
         <is>
-          <t>S6101 Edit S6101Clone</t>
+          <t>S6325 Edit S6325Clone</t>
         </is>
       </c>
       <c r="S19" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:15 pm</t>
+          <t>09/29/2026-05:42 pm</t>
         </is>
       </c>
       <c r="T19" s="0" t="inlineStr">
@@ -1769,7 +1759,7 @@
         </is>
       </c>
       <c r="U19" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V19" s="0" t="inlineStr">
         <is>
@@ -1778,36 +1768,31 @@
       </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>LUBABATU </t>
         </is>
       </c>
       <c r="Z19" s="0">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="AA19" s="0">
-        <v>138500</v>
+        <v>20000</v>
       </c>
       <c r="AB19" s="0">
-        <v>138500</v>
+        <v>20000</v>
       </c>
       <c r="AC19" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦138,500.00</t>
-        </is>
-      </c>
-      <c r="AD19" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦20,000.00</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:31">
       <c r="A20" s="0">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>Fantastic Holland</t>
+          <t>EMBELLISHED MDT</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
@@ -1817,20 +1802,20 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>YAYA SANI (3)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K20" s="0">
-        <v>8500</v>
+        <v>17000</v>
       </c>
       <c r="L20" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" s="0">
-        <v>25500</v>
+        <v>34000</v>
       </c>
       <c r="O20" s="0">
-        <v>25500</v>
+        <v>34000</v>
       </c>
       <c r="P20" s="0" t="inlineStr">
         <is>
@@ -1844,12 +1829,12 @@
       </c>
       <c r="R20" s="0" t="inlineStr">
         <is>
-          <t>S6101 Edit S6101Clone</t>
+          <t>S6326 Edit S6326Clone</t>
         </is>
       </c>
       <c r="S20" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:15 pm</t>
+          <t>09/29/2026-05:43 pm</t>
         </is>
       </c>
       <c r="T20" s="0" t="inlineStr">
@@ -1858,7 +1843,7 @@
         </is>
       </c>
       <c r="U20" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V20" s="0" t="inlineStr">
         <is>
@@ -1867,36 +1852,31 @@
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>Aisha Chic </t>
         </is>
       </c>
       <c r="Z20" s="0">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="AA20" s="0">
-        <v>138500</v>
+        <v>34000</v>
       </c>
       <c r="AB20" s="0">
-        <v>138500</v>
+        <v>34000</v>
       </c>
       <c r="AC20" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦138,500.00</t>
-        </is>
-      </c>
-      <c r="AD20" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦34,000.00</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:31">
       <c r="A21" s="0">
-        <v>214</v>
+        <v>96</v>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>Rotana holland</t>
+          <t>IMPERIAL GRAND SATIN</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -1906,20 +1886,20 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>YAYA SANI (3)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K21" s="0">
-        <v>8500</v>
+        <v>30000</v>
       </c>
       <c r="L21" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21" s="0">
-        <v>25500</v>
+        <v>60000</v>
       </c>
       <c r="O21" s="0">
-        <v>25500</v>
+        <v>60000</v>
       </c>
       <c r="P21" s="0" t="inlineStr">
         <is>
@@ -1933,12 +1913,12 @@
       </c>
       <c r="R21" s="0" t="inlineStr">
         <is>
-          <t>S6101 Edit S6101Clone</t>
+          <t>S6327 Edit S6327Clone</t>
         </is>
       </c>
       <c r="S21" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:15 pm</t>
+          <t>09/29/2026-05:43 pm</t>
         </is>
       </c>
       <c r="T21" s="0" t="inlineStr">
@@ -1947,7 +1927,7 @@
         </is>
       </c>
       <c r="U21" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V21" s="0" t="inlineStr">
         <is>
@@ -1956,41 +1936,36 @@
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>ZAINAB ZMY</t>
         </is>
       </c>
       <c r="Z21" s="0">
-        <v>23</v>
+        <v>370</v>
       </c>
       <c r="AA21" s="0">
-        <v>138500</v>
+        <v>60000</v>
       </c>
       <c r="AB21" s="0">
-        <v>138500</v>
+        <v>60000</v>
       </c>
       <c r="AC21" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦138,500.00</t>
-        </is>
-      </c>
-      <c r="AD21" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦60,000.00</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:31">
       <c r="A22" s="0">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>DIAMOND PLUS</t>
+          <t>CHIGANVY COTONOU PLAIN</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
@@ -1999,16 +1974,16 @@
         </is>
       </c>
       <c r="K22" s="0">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="L22" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N22" s="0">
-        <v>85000</v>
+        <v>19000</v>
       </c>
       <c r="O22" s="0">
-        <v>85000</v>
+        <v>19000</v>
       </c>
       <c r="P22" s="0" t="inlineStr">
         <is>
@@ -2022,12 +1997,12 @@
       </c>
       <c r="R22" s="0" t="inlineStr">
         <is>
-          <t>S6102 Edit S6102Clone</t>
+          <t>S6328 Edit S6328Clone</t>
         </is>
       </c>
       <c r="S22" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:40 pm</t>
+          <t>09/29/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T22" s="0" t="inlineStr">
@@ -2036,7 +2011,7 @@
         </is>
       </c>
       <c r="U22" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V22" s="0" t="inlineStr">
         <is>
@@ -2045,31 +2020,31 @@
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>MAMAN ASLAM </t>
+          <t>Haj Hadiza Pretty </t>
         </is>
       </c>
       <c r="Z22" s="0">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="AA22" s="0">
-        <v>85000</v>
+        <v>94000</v>
       </c>
       <c r="AB22" s="0">
-        <v>85000</v>
+        <v>94000</v>
       </c>
       <c r="AC22" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦85,000.00</t>
+          <t>Store Account: ₦94,000.00</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:31">
       <c r="A23" s="0">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTREE</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -2083,16 +2058,16 @@
         </is>
       </c>
       <c r="K23" s="0">
-        <v>10800</v>
+        <v>15000</v>
       </c>
       <c r="L23" s="0">
         <v>5</v>
       </c>
       <c r="N23" s="0">
-        <v>54000</v>
+        <v>75000</v>
       </c>
       <c r="O23" s="0">
-        <v>54000</v>
+        <v>75000</v>
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
@@ -2106,12 +2081,12 @@
       </c>
       <c r="R23" s="0" t="inlineStr">
         <is>
-          <t>S6103 Edit S6103Clone</t>
+          <t>S6328 Edit S6328Clone</t>
         </is>
       </c>
       <c r="S23" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:41 pm</t>
+          <t>09/29/2026-05:44 pm</t>
         </is>
       </c>
       <c r="T23" s="0" t="inlineStr">
@@ -2120,7 +2095,7 @@
         </is>
       </c>
       <c r="U23" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23" s="0" t="inlineStr">
         <is>
@@ -2129,36 +2104,36 @@
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>HAJ RABI </t>
+          <t>Haj Hadiza Pretty </t>
         </is>
       </c>
       <c r="Z23" s="0">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="AA23" s="0">
-        <v>54000</v>
+        <v>94000</v>
       </c>
       <c r="AB23" s="0">
-        <v>54000</v>
+        <v>94000</v>
       </c>
       <c r="AC23" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦54,000.00</t>
+          <t>Store Account: ₦94,000.00</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:31">
       <c r="A24" s="0">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE C</t>
+          <t>EMBELLISHED MDT</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
@@ -2167,16 +2142,16 @@
         </is>
       </c>
       <c r="K24" s="0">
-        <v>24000</v>
+        <v>17000</v>
       </c>
       <c r="L24" s="0">
         <v>1</v>
       </c>
       <c r="N24" s="0">
-        <v>24000</v>
+        <v>17000</v>
       </c>
       <c r="O24" s="0">
-        <v>24000</v>
+        <v>17000</v>
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
@@ -2190,12 +2165,12 @@
       </c>
       <c r="R24" s="0" t="inlineStr">
         <is>
-          <t>S6104 Edit S6104Clone</t>
+          <t>S6329 Edit S6329Clone</t>
         </is>
       </c>
       <c r="S24" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:42 pm</t>
+          <t>09/29/2026-05:45 pm</t>
         </is>
       </c>
       <c r="T24" s="0" t="inlineStr">
@@ -2204,7 +2179,7 @@
         </is>
       </c>
       <c r="U24" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V24" s="0" t="inlineStr">
         <is>
@@ -2213,88 +2188,83 @@
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
-          <t>Abba Tahir Shop </t>
+          <t>NURHAF </t>
         </is>
       </c>
       <c r="Z24" s="0">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="AA24" s="0">
-        <v>24000</v>
+        <v>46500</v>
       </c>
       <c r="AB24" s="0">
-        <v>24000</v>
+        <v>46500</v>
       </c>
       <c r="AC24" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦24,000.00</t>
-        </is>
-      </c>
-      <c r="AD24" s="0" t="inlineStr">
-        <is>
-          <t>BUHARI</t>
+          <t>Store Account: ₦46,500.00</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:31">
       <c r="A25" s="0">
-        <v>55</v>
+        <v>219</v>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>MADAM GRTZNER MEDIUM</t>
+          <t>Mandela kente Gold</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>HAFIZU TAHIR SHOP (5)</t>
         </is>
       </c>
       <c r="K25" s="0">
-        <v>7000</v>
+        <v>14500</v>
       </c>
       <c r="L25" s="0">
+        <v>1</v>
+      </c>
+      <c r="N25" s="0">
+        <v>14500</v>
+      </c>
+      <c r="O25" s="0">
+        <v>14500</v>
+      </c>
+      <c r="P25" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q25" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R25" s="0" t="inlineStr">
+        <is>
+          <t>S6329 Edit S6329Clone</t>
+        </is>
+      </c>
+      <c r="S25" s="0" t="inlineStr">
+        <is>
+          <t>09/29/2026-05:45 pm</t>
+        </is>
+      </c>
+      <c r="T25" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U25" s="0">
         <v>3</v>
       </c>
-      <c r="N25" s="0">
-        <v>21000</v>
-      </c>
-      <c r="O25" s="0">
-        <v>21000</v>
-      </c>
-      <c r="P25" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q25" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R25" s="0" t="inlineStr">
-        <is>
-          <t>S6105 Edit S6105Clone</t>
-        </is>
-      </c>
-      <c r="S25" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-04:42 pm</t>
-        </is>
-      </c>
-      <c r="T25" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U25" s="0">
-        <v>5</v>
-      </c>
       <c r="V25" s="0" t="inlineStr">
         <is>
           <t>BB </t>
@@ -2302,31 +2272,31 @@
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>Khalid Abasu Kala  </t>
+          <t>NURHAF </t>
         </is>
       </c>
       <c r="Z25" s="0">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="AA25" s="0">
-        <v>52000</v>
+        <v>46500</v>
       </c>
       <c r="AB25" s="0">
-        <v>52000</v>
+        <v>46500</v>
       </c>
       <c r="AC25" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦52,000.00</t>
+          <t>Store Account: ₦46,500.00</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:31">
       <c r="A26" s="0">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME STONE EMBELLISHED</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -2340,16 +2310,16 @@
         </is>
       </c>
       <c r="K26" s="0">
-        <v>19500</v>
+        <v>15000</v>
       </c>
       <c r="L26" s="0">
         <v>1</v>
       </c>
       <c r="N26" s="0">
-        <v>19500</v>
+        <v>15000</v>
       </c>
       <c r="O26" s="0">
-        <v>19500</v>
+        <v>15000</v>
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
@@ -2363,12 +2333,12 @@
       </c>
       <c r="R26" s="0" t="inlineStr">
         <is>
-          <t>S6105 Edit S6105Clone</t>
+          <t>S6329 Edit S6329Clone</t>
         </is>
       </c>
       <c r="S26" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:42 pm</t>
+          <t>09/29/2026-05:45 pm</t>
         </is>
       </c>
       <c r="T26" s="0" t="inlineStr">
@@ -2377,7 +2347,7 @@
         </is>
       </c>
       <c r="U26" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V26" s="0" t="inlineStr">
         <is>
@@ -2386,31 +2356,31 @@
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>Khalid Abasu Kala  </t>
+          <t>NURHAF </t>
         </is>
       </c>
       <c r="Z26" s="0">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="AA26" s="0">
-        <v>52000</v>
+        <v>46500</v>
       </c>
       <c r="AB26" s="0">
-        <v>52000</v>
+        <v>46500</v>
       </c>
       <c r="AC26" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦52,000.00</t>
+          <t>Store Account: ₦46,500.00</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:31">
       <c r="A27" s="0">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>HOLLAND MEDIUM</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -2424,16 +2394,16 @@
         </is>
       </c>
       <c r="K27" s="0">
-        <v>11500</v>
+        <v>15500</v>
       </c>
       <c r="L27" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N27" s="0">
-        <v>11500</v>
+        <v>46500</v>
       </c>
       <c r="O27" s="0">
-        <v>11500</v>
+        <v>46500</v>
       </c>
       <c r="P27" s="0" t="inlineStr">
         <is>
@@ -2447,12 +2417,12 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>S6105 Edit S6105Clone</t>
+          <t>S6330 Edit S6330Clone</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:42 pm</t>
+          <t>09/29/2026-05:46 pm</t>
         </is>
       </c>
       <c r="T27" s="0" t="inlineStr">
@@ -2461,7 +2431,7 @@
         </is>
       </c>
       <c r="U27" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V27" s="0" t="inlineStr">
         <is>
@@ -2470,54 +2440,54 @@
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>Khalid Abasu Kala  </t>
+          <t>MARIA BOSE</t>
         </is>
       </c>
       <c r="Z27" s="0">
-        <v>51</v>
+        <v>295</v>
       </c>
       <c r="AA27" s="0">
-        <v>52000</v>
+        <v>46500</v>
       </c>
       <c r="AB27" s="0">
-        <v>52000</v>
+        <v>46500</v>
       </c>
       <c r="AC27" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦52,000.00</t>
+          <t>ACCESS BANK: ₦46,500.00</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:31">
       <c r="A28" s="0">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>TYCOON AND GAZA WOOL</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K28" s="0">
-        <v>14800</v>
+        <v>5000</v>
       </c>
       <c r="L28" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N28" s="0">
-        <v>29600</v>
+        <v>40000</v>
       </c>
       <c r="O28" s="0">
-        <v>29600</v>
+        <v>40000</v>
       </c>
       <c r="P28" s="0" t="inlineStr">
         <is>
@@ -2531,12 +2501,12 @@
       </c>
       <c r="R28" s="0" t="inlineStr">
         <is>
-          <t>S6106 Edit S6106Clone</t>
+          <t>S6331 Edit S6331Clone</t>
         </is>
       </c>
       <c r="S28" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:43 pm</t>
+          <t>09/29/2026-05:46 pm</t>
         </is>
       </c>
       <c r="T28" s="0" t="inlineStr">
@@ -2545,7 +2515,7 @@
         </is>
       </c>
       <c r="U28" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V28" s="0" t="inlineStr">
         <is>
@@ -2554,31 +2524,36 @@
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>SHAMSIYYAH MUHD</t>
+          <t>Abba Tahir Shop </t>
         </is>
       </c>
       <c r="Z28" s="0">
-        <v>257</v>
+        <v>24</v>
       </c>
       <c r="AA28" s="0">
-        <v>29600</v>
+        <v>40000</v>
       </c>
       <c r="AB28" s="0">
-        <v>29600</v>
+        <v>40000</v>
       </c>
       <c r="AC28" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦29,600.00</t>
+          <t>ACCESS BANK: ₦40,000.00</t>
+        </is>
+      </c>
+      <c r="AD28" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:31">
       <c r="A29" s="0">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>HOLLANTEX GOLD STONE</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -2592,16 +2567,16 @@
         </is>
       </c>
       <c r="K29" s="0">
-        <v>13500</v>
+        <v>19500</v>
       </c>
       <c r="L29" s="0">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="N29" s="0">
-        <v>1188000</v>
+        <v>19500</v>
       </c>
       <c r="O29" s="0">
-        <v>1188000</v>
+        <v>19500</v>
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
@@ -2615,12 +2590,12 @@
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t>S6107 Edit S6107Clone</t>
+          <t>S6332 Edit S6332Clone</t>
         </is>
       </c>
       <c r="S29" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:43 pm</t>
+          <t>09/29/2026-05:47 pm</t>
         </is>
       </c>
       <c r="T29" s="0" t="inlineStr">
@@ -2629,7 +2604,7 @@
         </is>
       </c>
       <c r="U29" s="0">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="V29" s="0" t="inlineStr">
         <is>
@@ -2638,31 +2613,31 @@
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>ESHA ALPHA</t>
+          <t>Khalid Abasu Kala  </t>
         </is>
       </c>
       <c r="Z29" s="0">
-        <v>355</v>
+        <v>51</v>
       </c>
       <c r="AA29" s="0">
-        <v>1188000</v>
+        <v>96000</v>
       </c>
       <c r="AB29" s="0">
-        <v>1188000</v>
+        <v>96000</v>
       </c>
       <c r="AC29" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦1,188,000.00</t>
+          <t>ACCESS BANK: ₦62,000.00ACCESS BANK: ₦34,000.00</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:31">
       <c r="A30" s="0">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTEX EMBELLISHED</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
@@ -2676,16 +2651,16 @@
         </is>
       </c>
       <c r="K30" s="0">
-        <v>18000</v>
+        <v>15500</v>
       </c>
       <c r="L30" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N30" s="0">
-        <v>18000</v>
+        <v>62000</v>
       </c>
       <c r="O30" s="0">
-        <v>18000</v>
+        <v>62000</v>
       </c>
       <c r="P30" s="0" t="inlineStr">
         <is>
@@ -2699,12 +2674,12 @@
       </c>
       <c r="R30" s="0" t="inlineStr">
         <is>
-          <t>S6108 Edit S6108Clone</t>
+          <t>S6332 Edit S6332Clone</t>
         </is>
       </c>
       <c r="S30" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:44 pm</t>
+          <t>09/29/2026-05:47 pm</t>
         </is>
       </c>
       <c r="T30" s="0" t="inlineStr">
@@ -2713,7 +2688,7 @@
         </is>
       </c>
       <c r="U30" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V30" s="0" t="inlineStr">
         <is>
@@ -2722,31 +2697,31 @@
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>RAHAMA BAMALLI</t>
+          <t>Khalid Abasu Kala  </t>
         </is>
       </c>
       <c r="Z30" s="0">
-        <v>265</v>
+        <v>51</v>
       </c>
       <c r="AA30" s="0">
-        <v>33000</v>
+        <v>96000</v>
       </c>
       <c r="AB30" s="0">
-        <v>33000</v>
+        <v>96000</v>
       </c>
       <c r="AC30" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦33,000.00</t>
+          <t>ACCESS BANK: ₦62,000.00ACCESS BANK: ₦34,000.00</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:31">
       <c r="A31" s="0">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>Mandela kente Gold</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
@@ -2756,20 +2731,20 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>HAFIZU TAHIR SHOP (5)</t>
         </is>
       </c>
       <c r="K31" s="0">
-        <v>15000</v>
+        <v>14500</v>
       </c>
       <c r="L31" s="0">
         <v>1</v>
       </c>
       <c r="N31" s="0">
-        <v>15000</v>
+        <v>14500</v>
       </c>
       <c r="O31" s="0">
-        <v>15000</v>
+        <v>14500</v>
       </c>
       <c r="P31" s="0" t="inlineStr">
         <is>
@@ -2783,12 +2758,12 @@
       </c>
       <c r="R31" s="0" t="inlineStr">
         <is>
-          <t>S6108 Edit S6108Clone</t>
+          <t>S6332 Edit S6332Clone</t>
         </is>
       </c>
       <c r="S31" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:44 pm</t>
+          <t>09/29/2026-05:47 pm</t>
         </is>
       </c>
       <c r="T31" s="0" t="inlineStr">
@@ -2797,7 +2772,7 @@
         </is>
       </c>
       <c r="U31" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V31" s="0" t="inlineStr">
         <is>
@@ -2806,31 +2781,31 @@
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>RAHAMA BAMALLI</t>
+          <t>Khalid Abasu Kala  </t>
         </is>
       </c>
       <c r="Z31" s="0">
-        <v>265</v>
+        <v>51</v>
       </c>
       <c r="AA31" s="0">
-        <v>33000</v>
+        <v>96000</v>
       </c>
       <c r="AB31" s="0">
-        <v>33000</v>
+        <v>96000</v>
       </c>
       <c r="AC31" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦33,000.00</t>
+          <t>ACCESS BANK: ₦62,000.00ACCESS BANK: ₦34,000.00</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:31">
       <c r="A32" s="0">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>HOLLANTEX GOLD STONE</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
@@ -2840,20 +2815,20 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K32" s="0">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="L32" s="0">
         <v>1</v>
       </c>
       <c r="N32" s="0">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="O32" s="0">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="P32" s="0" t="inlineStr">
         <is>
@@ -2867,12 +2842,12 @@
       </c>
       <c r="R32" s="0" t="inlineStr">
         <is>
-          <t>S6109 Edit S6109Clone</t>
+          <t>S6333 Edit S6333Clone</t>
         </is>
       </c>
       <c r="S32" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:44 pm</t>
+          <t>09/29/2026-05:48 pm</t>
         </is>
       </c>
       <c r="T32" s="0" t="inlineStr">
@@ -2890,54 +2865,54 @@
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>RABI'ATU SULAIMAN</t>
+          <t>MARYAM FAGGO</t>
         </is>
       </c>
       <c r="Z32" s="0">
-        <v>356</v>
+        <v>204</v>
       </c>
       <c r="AA32" s="0">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="AB32" s="0">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="AC32" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦15,000.00</t>
+          <t>ACCESS BANK: ₦20,000.00</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:31">
       <c r="A33" s="0">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>LONGHUA YARD COLLECTION</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K33" s="0">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="L33" s="0">
         <v>4</v>
       </c>
       <c r="N33" s="0">
-        <v>60000</v>
+        <v>14000</v>
       </c>
       <c r="O33" s="0">
-        <v>60000</v>
+        <v>14000</v>
       </c>
       <c r="P33" s="0" t="inlineStr">
         <is>
@@ -2951,12 +2926,12 @@
       </c>
       <c r="R33" s="0" t="inlineStr">
         <is>
-          <t>S6110 Edit S6110Clone</t>
+          <t>S6334 Edit S6334Clone</t>
         </is>
       </c>
       <c r="S33" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:45 pm</t>
+          <t>09/29/2026-05:48 pm</t>
         </is>
       </c>
       <c r="T33" s="0" t="inlineStr">
@@ -2981,29 +2956,29 @@
         <v>24</v>
       </c>
       <c r="AA33" s="0">
-        <v>60000</v>
+        <v>14000</v>
       </c>
       <c r="AB33" s="0">
-        <v>60000</v>
+        <v>14000</v>
       </c>
       <c r="AC33" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦60,000.00</t>
+          <t>ACCESS BANK: ₦14,000.00</t>
         </is>
       </c>
       <c r="AD33" s="0" t="inlineStr">
         <is>
-          <t>FAIZA BAUCHI</t>
+          <t>ABBA TAHIR</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:31">
       <c r="A34" s="0">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
@@ -3017,16 +2992,16 @@
         </is>
       </c>
       <c r="K34" s="0">
-        <v>14500</v>
+        <v>15500</v>
       </c>
       <c r="L34" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" s="0">
-        <v>43500</v>
+        <v>31000</v>
       </c>
       <c r="O34" s="0">
-        <v>43500</v>
+        <v>31000</v>
       </c>
       <c r="P34" s="0" t="inlineStr">
         <is>
@@ -3040,12 +3015,12 @@
       </c>
       <c r="R34" s="0" t="inlineStr">
         <is>
-          <t>S6111 Edit S6111Clone</t>
+          <t>S6335 Edit S6335Clone</t>
         </is>
       </c>
       <c r="S34" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:49 pm</t>
+          <t>09/29/2026-05:49 pm</t>
         </is>
       </c>
       <c r="T34" s="0" t="inlineStr">
@@ -3054,7 +3029,7 @@
         </is>
       </c>
       <c r="U34" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V34" s="0" t="inlineStr">
         <is>
@@ -3063,31 +3038,31 @@
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>M KHADIJA LABARAN</t>
+          <t>JAMILA KADUNA </t>
         </is>
       </c>
       <c r="Z34" s="0">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="AA34" s="0">
-        <v>43500</v>
+        <v>31000</v>
       </c>
       <c r="AB34" s="0">
-        <v>43500</v>
+        <v>31000</v>
       </c>
       <c r="AC34" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦43,500.00</t>
+          <t>ACCESS BANK: ₦31,000.00</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:31">
       <c r="A35" s="0">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
@@ -3101,16 +3076,16 @@
         </is>
       </c>
       <c r="K35" s="0">
-        <v>19500</v>
+        <v>16000</v>
       </c>
       <c r="L35" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N35" s="0">
-        <v>58500</v>
+        <v>16000</v>
       </c>
       <c r="O35" s="0">
-        <v>58500</v>
+        <v>16000</v>
       </c>
       <c r="P35" s="0" t="inlineStr">
         <is>
@@ -3124,12 +3099,12 @@
       </c>
       <c r="R35" s="0" t="inlineStr">
         <is>
-          <t>S6112 Edit S6112Clone</t>
+          <t>S6336 Edit S6336Clone</t>
         </is>
       </c>
       <c r="S35" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:50 pm</t>
+          <t>09/29/2026-05:51 pm</t>
         </is>
       </c>
       <c r="T35" s="0" t="inlineStr">
@@ -3138,7 +3113,7 @@
         </is>
       </c>
       <c r="U35" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V35" s="0" t="inlineStr">
         <is>
@@ -3147,31 +3122,31 @@
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>AISHA JARMA</t>
+          <t>RABI'ATU SULAIMAN</t>
         </is>
       </c>
       <c r="Z35" s="0">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="AA35" s="0">
-        <v>58500</v>
+        <v>16000</v>
       </c>
       <c r="AB35" s="0">
-        <v>58500</v>
+        <v>16000</v>
       </c>
       <c r="AC35" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦58,500.00</t>
+          <t>ACCESS BANK: ₦16,000.00</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:31">
       <c r="A36" s="0">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>ATAMPA LACE MIX AND MATCH</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
@@ -3185,16 +3160,16 @@
         </is>
       </c>
       <c r="K36" s="0">
-        <v>15000</v>
+        <v>55000</v>
       </c>
       <c r="L36" s="0">
         <v>1</v>
       </c>
       <c r="N36" s="0">
-        <v>15000</v>
+        <v>55000</v>
       </c>
       <c r="O36" s="0">
-        <v>15000</v>
+        <v>55000</v>
       </c>
       <c r="P36" s="0" t="inlineStr">
         <is>
@@ -3208,12 +3183,12 @@
       </c>
       <c r="R36" s="0" t="inlineStr">
         <is>
-          <t>S6113 Edit S6113Clone</t>
+          <t>S6337 Edit S6337Clone</t>
         </is>
       </c>
       <c r="S36" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:50 pm</t>
+          <t>09/29/2026-05:51 pm</t>
         </is>
       </c>
       <c r="T36" s="0" t="inlineStr">
@@ -3222,7 +3197,7 @@
         </is>
       </c>
       <c r="U36" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36" s="0" t="inlineStr">
         <is>
@@ -3231,54 +3206,54 @@
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>AISHA HAFIZ</t>
+          <t>AISHA JARMA</t>
         </is>
       </c>
       <c r="Z36" s="0">
-        <v>357</v>
+        <v>274</v>
       </c>
       <c r="AA36" s="0">
-        <v>30000</v>
+        <v>55000</v>
       </c>
       <c r="AB36" s="0">
-        <v>30000</v>
+        <v>55000</v>
       </c>
       <c r="AC36" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦30,000.00</t>
+          <t>ACCESS BANK: ₦55,000.00</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:31">
       <c r="A37" s="0">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>MADAM GRTZNER MEDIUM</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K37" s="0">
-        <v>15000</v>
+        <v>6500</v>
       </c>
       <c r="L37" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N37" s="0">
-        <v>15000</v>
+        <v>58500</v>
       </c>
       <c r="O37" s="0">
-        <v>15000</v>
+        <v>58500</v>
       </c>
       <c r="P37" s="0" t="inlineStr">
         <is>
@@ -3292,12 +3267,12 @@
       </c>
       <c r="R37" s="0" t="inlineStr">
         <is>
-          <t>S6113 Edit S6113Clone</t>
+          <t>S6338 Edit S6338Clone</t>
         </is>
       </c>
       <c r="S37" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:50 pm</t>
+          <t>09/29/2026-05:52 pm</t>
         </is>
       </c>
       <c r="T37" s="0" t="inlineStr">
@@ -3306,7 +3281,7 @@
         </is>
       </c>
       <c r="U37" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V37" s="0" t="inlineStr">
         <is>
@@ -3315,31 +3290,36 @@
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>AISHA HAFIZ</t>
+          <t>Abba Tahir Shop </t>
         </is>
       </c>
       <c r="Z37" s="0">
-        <v>357</v>
+        <v>24</v>
       </c>
       <c r="AA37" s="0">
-        <v>30000</v>
+        <v>58500</v>
       </c>
       <c r="AB37" s="0">
-        <v>30000</v>
+        <v>58500</v>
       </c>
       <c r="AC37" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦30,000.00</t>
+          <t>ACCESS BANK: ₦58,500.00</t>
+        </is>
+      </c>
+      <c r="AD37" s="0" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:31">
       <c r="A38" s="0">
-        <v>104</v>
+        <v>201</v>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTTON POPLIN</t>
+          <t>Hollantex Mix pattern</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
@@ -3353,16 +3333,16 @@
         </is>
       </c>
       <c r="K38" s="0">
-        <v>27000</v>
+        <v>14500</v>
       </c>
       <c r="L38" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N38" s="0">
-        <v>27000</v>
+        <v>145000</v>
       </c>
       <c r="O38" s="0">
-        <v>27000</v>
+        <v>145000</v>
       </c>
       <c r="P38" s="0" t="inlineStr">
         <is>
@@ -3376,12 +3356,12 @@
       </c>
       <c r="R38" s="0" t="inlineStr">
         <is>
-          <t>S6114 Edit S6114Clone</t>
+          <t>S6339 Edit S6339Clone</t>
         </is>
       </c>
       <c r="S38" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:51 pm</t>
+          <t>09/29/2026-05:54 pm</t>
         </is>
       </c>
       <c r="T38" s="0" t="inlineStr">
@@ -3390,7 +3370,7 @@
         </is>
       </c>
       <c r="U38" s="0">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="V38" s="0" t="inlineStr">
         <is>
@@ -3399,31 +3379,31 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>HAJ RUKAYYA YUSUF</t>
+          <t>HAJ MAIMUNA PUNDIT </t>
         </is>
       </c>
       <c r="Z38" s="0">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="AA38" s="0">
-        <v>27000</v>
+        <v>205000</v>
       </c>
       <c r="AB38" s="0">
-        <v>27000</v>
+        <v>205000</v>
       </c>
       <c r="AC38" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦27,000.00</t>
+          <t>ACCESS BANK: ₦205,000.00</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:31">
       <c r="A39" s="0">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>Luxe Embellished MD</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
@@ -3437,16 +3417,16 @@
         </is>
       </c>
       <c r="K39" s="0">
-        <v>16500</v>
+        <v>15000</v>
       </c>
       <c r="L39" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N39" s="0">
-        <v>33000</v>
+        <v>60000</v>
       </c>
       <c r="O39" s="0">
-        <v>33000</v>
+        <v>60000</v>
       </c>
       <c r="P39" s="0" t="inlineStr">
         <is>
@@ -3460,12 +3440,12 @@
       </c>
       <c r="R39" s="0" t="inlineStr">
         <is>
-          <t>S6115 Edit S6115Clone</t>
+          <t>S6339 Edit S6339Clone</t>
         </is>
       </c>
       <c r="S39" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:55 pm</t>
+          <t>09/29/2026-05:54 pm</t>
         </is>
       </c>
       <c r="T39" s="0" t="inlineStr">
@@ -3474,7 +3454,7 @@
         </is>
       </c>
       <c r="U39" s="0">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="V39" s="0" t="inlineStr">
         <is>
@@ -3483,36 +3463,36 @@
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>RAHAMA BAMALLI</t>
+          <t>HAJ MAIMUNA PUNDIT </t>
         </is>
       </c>
       <c r="Z39" s="0">
-        <v>265</v>
+        <v>201</v>
       </c>
       <c r="AA39" s="0">
-        <v>33000</v>
+        <v>205000</v>
       </c>
       <c r="AB39" s="0">
-        <v>33000</v>
+        <v>205000</v>
       </c>
       <c r="AC39" s="0" t="inlineStr">
         <is>
-          <t>ACCESS BANK: ₦33,000.00</t>
+          <t>ACCESS BANK: ₦205,000.00</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:31">
       <c r="A40" s="0">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE D</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
@@ -3521,16 +3501,16 @@
         </is>
       </c>
       <c r="K40" s="0">
-        <v>23000</v>
+        <v>15500</v>
       </c>
       <c r="L40" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N40" s="0">
-        <v>69000</v>
+        <v>77500</v>
       </c>
       <c r="O40" s="0">
-        <v>69000</v>
+        <v>77500</v>
       </c>
       <c r="P40" s="0" t="inlineStr">
         <is>
@@ -3544,12 +3524,12 @@
       </c>
       <c r="R40" s="0" t="inlineStr">
         <is>
-          <t>S6116 Edit S6116Clone</t>
+          <t>S6340 Edit S6340Clone</t>
         </is>
       </c>
       <c r="S40" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:56 pm</t>
+          <t>09/29/2026-05:54 pm</t>
         </is>
       </c>
       <c r="T40" s="0" t="inlineStr">
@@ -3558,7 +3538,7 @@
         </is>
       </c>
       <c r="U40" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V40" s="0" t="inlineStr">
         <is>
@@ -3567,36 +3547,36 @@
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>Abba Tahir Shop </t>
         </is>
       </c>
       <c r="Z40" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA40" s="0">
-        <v>69000</v>
+        <v>77500</v>
       </c>
       <c r="AB40" s="0">
-        <v>69000</v>
+        <v>77500</v>
       </c>
       <c r="AC40" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦69,000.00</t>
+          <t>ACCESS BANK: ₦77,500.00</t>
         </is>
       </c>
       <c r="AD40" s="0" t="inlineStr">
         <is>
-          <t>AZA</t>
+          <t>HAJ LAILA</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:31">
       <c r="A41" s="0">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>JULIUS EMBELLISHED </t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
@@ -3610,16 +3590,16 @@
         </is>
       </c>
       <c r="K41" s="0">
-        <v>83000</v>
+        <v>15500</v>
       </c>
       <c r="L41" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N41" s="0">
-        <v>83000</v>
+        <v>46500</v>
       </c>
       <c r="O41" s="0">
-        <v>83000</v>
+        <v>46500</v>
       </c>
       <c r="P41" s="0" t="inlineStr">
         <is>
@@ -3633,12 +3613,12 @@
       </c>
       <c r="R41" s="0" t="inlineStr">
         <is>
-          <t>S6117 Edit S6117Clone</t>
+          <t>S6341 Edit S6341Clone</t>
         </is>
       </c>
       <c r="S41" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:56 pm</t>
+          <t>09/29/2026-05:55 pm</t>
         </is>
       </c>
       <c r="T41" s="0" t="inlineStr">
@@ -3647,7 +3627,7 @@
         </is>
       </c>
       <c r="U41" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V41" s="0" t="inlineStr">
         <is>
@@ -3656,36 +3636,36 @@
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>Mustapha Shop </t>
+          <t>Waleed Shop </t>
         </is>
       </c>
       <c r="Z41" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA41" s="0">
-        <v>83000</v>
+        <v>46500</v>
       </c>
       <c r="AB41" s="0">
-        <v>83000</v>
+        <v>46500</v>
       </c>
       <c r="AC41" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦83,000.00</t>
+          <t>MONIEPOINT: ₦46,500.00</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:31">
       <c r="A42" s="0">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTTON POPLIN</t>
+          <t>RIGHTMAN AND WISEMAN</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
@@ -3694,16 +3674,16 @@
         </is>
       </c>
       <c r="K42" s="0">
-        <v>26000</v>
+        <v>5000</v>
       </c>
       <c r="L42" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N42" s="0">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="O42" s="0">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
@@ -3717,12 +3697,12 @@
       </c>
       <c r="R42" s="0" t="inlineStr">
         <is>
-          <t>S6118 Edit S6118Clone</t>
+          <t>S6342 Edit S6342Clone</t>
         </is>
       </c>
       <c r="S42" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:57 pm</t>
+          <t>09/29/2026-05:55 pm</t>
         </is>
       </c>
       <c r="T42" s="0" t="inlineStr">
@@ -3731,7 +3711,7 @@
         </is>
       </c>
       <c r="U42" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V42" s="0" t="inlineStr">
         <is>
@@ -3740,36 +3720,36 @@
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>Ibrahim BB Jafar (1522263645)</t>
+        </is>
+      </c>
+      <c r="Y42" s="0" t="inlineStr">
+        <is>
+          <t>08146595795</t>
         </is>
       </c>
       <c r="Z42" s="0">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="AA42" s="0">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="AB42" s="0">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="AC42" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦26,000.00</t>
-        </is>
-      </c>
-      <c r="AD42" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>MONIEPOINT: ₦15,000.00</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:31">
       <c r="A43" s="0">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>CHIGANVY INDIA</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
@@ -3783,16 +3763,16 @@
         </is>
       </c>
       <c r="K43" s="0">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="L43" s="0">
         <v>2</v>
       </c>
       <c r="N43" s="0">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="O43" s="0">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="P43" s="0" t="inlineStr">
         <is>
@@ -3806,12 +3786,12 @@
       </c>
       <c r="R43" s="0" t="inlineStr">
         <is>
-          <t>S6119 Edit S6119Clone</t>
+          <t>S6343 Edit S6343Clone</t>
         </is>
       </c>
       <c r="S43" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:57 pm</t>
+          <t>09/29/2026-05:56 pm</t>
         </is>
       </c>
       <c r="T43" s="0" t="inlineStr">
@@ -3820,7 +3800,7 @@
         </is>
       </c>
       <c r="U43" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V43" s="0" t="inlineStr">
         <is>
@@ -3829,36 +3809,31 @@
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>MUSA GARBA</t>
         </is>
       </c>
       <c r="Z43" s="0">
-        <v>23</v>
+        <v>214</v>
       </c>
       <c r="AA43" s="0">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="AB43" s="0">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="AC43" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦30,000.00</t>
-        </is>
-      </c>
-      <c r="AD43" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Cash: ₦20,000.00MONIEPOINT: ₦25,000.00</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:31">
       <c r="A44" s="0">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
@@ -3872,16 +3847,16 @@
         </is>
       </c>
       <c r="K44" s="0">
-        <v>16500</v>
+        <v>15000</v>
       </c>
       <c r="L44" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N44" s="0">
-        <v>82500</v>
+        <v>30000</v>
       </c>
       <c r="O44" s="0">
-        <v>82500</v>
+        <v>30000</v>
       </c>
       <c r="P44" s="0" t="inlineStr">
         <is>
@@ -3895,12 +3870,12 @@
       </c>
       <c r="R44" s="0" t="inlineStr">
         <is>
-          <t>S6120 Edit S6120Clone</t>
+          <t>S6343 Edit S6343Clone</t>
         </is>
       </c>
       <c r="S44" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:58 pm</t>
+          <t>09/29/2026-05:56 pm</t>
         </is>
       </c>
       <c r="T44" s="0" t="inlineStr">
@@ -3909,7 +3884,7 @@
         </is>
       </c>
       <c r="U44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V44" s="0" t="inlineStr">
         <is>
@@ -3918,36 +3893,31 @@
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>Tahir Walk-in Customers </t>
+          <t>MUSA GARBA</t>
         </is>
       </c>
       <c r="Z44" s="0">
-        <v>23</v>
+        <v>214</v>
       </c>
       <c r="AA44" s="0">
-        <v>82500</v>
+        <v>45000</v>
       </c>
       <c r="AB44" s="0">
-        <v>82500</v>
+        <v>45000</v>
       </c>
       <c r="AC44" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦82,500.00</t>
-        </is>
-      </c>
-      <c r="AD44" s="0" t="inlineStr">
-        <is>
-          <t>SHAMSU AR</t>
+          <t>Cash: ₦20,000.00MONIEPOINT: ₦25,000.00</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:31">
       <c r="A45" s="0">
-        <v>104</v>
+        <v>201</v>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTTON POPLIN</t>
+          <t>Hollantex Mix pattern</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
@@ -3961,16 +3931,16 @@
         </is>
       </c>
       <c r="K45" s="0">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="L45" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N45" s="0">
-        <v>52000</v>
+        <v>15000</v>
       </c>
       <c r="O45" s="0">
-        <v>52000</v>
+        <v>15000</v>
       </c>
       <c r="P45" s="0" t="inlineStr">
         <is>
@@ -3984,12 +3954,12 @@
       </c>
       <c r="R45" s="0" t="inlineStr">
         <is>
-          <t>S6121 Edit S6121Clone</t>
+          <t>S6344 Edit S6344Clone</t>
         </is>
       </c>
       <c r="S45" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-04:59 pm</t>
+          <t>09/29/2026-05:57 pm</t>
         </is>
       </c>
       <c r="T45" s="0" t="inlineStr">
@@ -3998,7 +3968,7 @@
         </is>
       </c>
       <c r="U45" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V45" s="0" t="inlineStr">
         <is>
@@ -4014,29 +3984,29 @@
         <v>23</v>
       </c>
       <c r="AA45" s="0">
-        <v>52000</v>
+        <v>15000</v>
       </c>
       <c r="AB45" s="0">
-        <v>52000</v>
+        <v>15000</v>
       </c>
       <c r="AC45" s="0" t="inlineStr">
         <is>
-          <t>MONIEPOINT: ₦52,000.00</t>
+          <t>MONIEPOINT: ₦15,000.00</t>
         </is>
       </c>
       <c r="AD45" s="0" t="inlineStr">
         <is>
-          <t>CTM</t>
+          <t>ctm</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:31">
       <c r="A46" s="0">
-        <v>219</v>
+        <v>118</v>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>PRESTIGE EMBELLISHED</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
@@ -4046,20 +4016,20 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K46" s="0">
-        <v>14500</v>
+        <v>17000</v>
       </c>
       <c r="L46" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N46" s="0">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="O46" s="0">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="P46" s="0" t="inlineStr">
         <is>
@@ -4073,12 +4043,12 @@
       </c>
       <c r="R46" s="0" t="inlineStr">
         <is>
-          <t>S6122 Edit S6122Clone</t>
+          <t>S6345 Edit S6345Clone</t>
         </is>
       </c>
       <c r="S46" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:11 pm</t>
+          <t>09/29/2026-05:58 pm</t>
         </is>
       </c>
       <c r="T46" s="0" t="inlineStr">
@@ -4087,7 +4057,7 @@
         </is>
       </c>
       <c r="U46" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V46" s="0" t="inlineStr">
         <is>
@@ -4096,31 +4066,36 @@
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>Haj Hadiza Pretty </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z46" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AA46" s="0">
-        <v>29000</v>
+        <v>56000</v>
       </c>
       <c r="AB46" s="0">
-        <v>29000</v>
+        <v>56000</v>
       </c>
       <c r="AC46" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦29,000.00</t>
+          <t>MONIEPOINT: ₦56,000.00</t>
+        </is>
+      </c>
+      <c r="AD46" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:31">
       <c r="A47" s="0">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>HOLLAND MEDIUM</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
@@ -4134,16 +4109,16 @@
         </is>
       </c>
       <c r="K47" s="0">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="L47" s="0">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N47" s="0">
-        <v>84000</v>
+        <v>24000</v>
       </c>
       <c r="O47" s="0">
-        <v>84000</v>
+        <v>24000</v>
       </c>
       <c r="P47" s="0" t="inlineStr">
         <is>
@@ -4157,12 +4132,12 @@
       </c>
       <c r="R47" s="0" t="inlineStr">
         <is>
-          <t>S6123 Edit S6123Clone</t>
+          <t>S6345 Edit S6345Clone</t>
         </is>
       </c>
       <c r="S47" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:12 pm</t>
+          <t>09/29/2026-05:58 pm</t>
         </is>
       </c>
       <c r="T47" s="0" t="inlineStr">
@@ -4171,7 +4146,7 @@
         </is>
       </c>
       <c r="U47" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V47" s="0" t="inlineStr">
         <is>
@@ -4180,54 +4155,59 @@
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>UMMI MUMTAZ</t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z47" s="0">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AA47" s="0">
-        <v>84000</v>
+        <v>56000</v>
       </c>
       <c r="AB47" s="0">
-        <v>84000</v>
+        <v>56000</v>
       </c>
       <c r="AC47" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦84,000.00</t>
+          <t>MONIEPOINT: ₦56,000.00</t>
+        </is>
+      </c>
+      <c r="AD47" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:31">
       <c r="A48" s="0">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>Baby Blueberry Material</t>
+          <t>Super English ABC</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>FAHAD TAHIR (2)</t>
         </is>
       </c>
       <c r="K48" s="0">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="L48" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" s="0">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="O48" s="0">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="P48" s="0" t="inlineStr">
         <is>
@@ -4241,12 +4221,12 @@
       </c>
       <c r="R48" s="0" t="inlineStr">
         <is>
-          <t>S6124 Edit S6124Clone</t>
+          <t>S6345 Edit S6345Clone</t>
         </is>
       </c>
       <c r="S48" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:12 pm</t>
+          <t>09/29/2026-05:58 pm</t>
         </is>
       </c>
       <c r="T48" s="0" t="inlineStr">
@@ -4255,7 +4235,7 @@
         </is>
       </c>
       <c r="U48" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V48" s="0" t="inlineStr">
         <is>
@@ -4264,59 +4244,59 @@
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z48" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA48" s="0">
-        <v>28000</v>
+        <v>56000</v>
       </c>
       <c r="AB48" s="0">
-        <v>28000</v>
+        <v>56000</v>
       </c>
       <c r="AC48" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦28,000.00</t>
+          <t>MONIEPOINT: ₦56,000.00</t>
         </is>
       </c>
       <c r="AD48" s="0" t="inlineStr">
         <is>
-          <t>SHAFA'ATU SHEHU</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:31">
       <c r="A49" s="0">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>Mesh luxury lace</t>
+          <t>Fantastic Holland</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>FAHAD TAHIR (2)</t>
+          <t>YAYA SANI (3)</t>
         </is>
       </c>
       <c r="K49" s="0">
-        <v>250000</v>
+        <v>8300</v>
       </c>
       <c r="L49" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N49" s="0">
-        <v>250000</v>
+        <v>49800</v>
       </c>
       <c r="O49" s="0">
-        <v>250000</v>
+        <v>49800</v>
       </c>
       <c r="P49" s="0" t="inlineStr">
         <is>
@@ -4330,12 +4310,12 @@
       </c>
       <c r="R49" s="0" t="inlineStr">
         <is>
-          <t>S6125 Edit S6125Clone</t>
+          <t>S6346 Edit S6346Clone</t>
         </is>
       </c>
       <c r="S49" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:13 pm</t>
+          <t>09/29/2026-05:58 pm</t>
         </is>
       </c>
       <c r="T49" s="0" t="inlineStr">
@@ -4344,7 +4324,7 @@
         </is>
       </c>
       <c r="U49" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V49" s="0" t="inlineStr">
         <is>
@@ -4353,31 +4333,31 @@
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>Jamila Baba </t>
+          <t>Kaby Daura Shop </t>
         </is>
       </c>
       <c r="Z49" s="0">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AA49" s="0">
-        <v>250000</v>
+        <v>49800</v>
       </c>
       <c r="AB49" s="0">
-        <v>250000</v>
+        <v>49800</v>
       </c>
       <c r="AC49" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦250,000.00</t>
+          <t>MONIEPOINT: ₦49,800.00</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:31">
       <c r="A50" s="0">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>GLITTER ROBA </t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
@@ -4387,20 +4367,20 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K50" s="0">
-        <v>14500</v>
+        <v>5400</v>
       </c>
       <c r="L50" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N50" s="0">
-        <v>145000</v>
+        <v>16200</v>
       </c>
       <c r="O50" s="0">
-        <v>145000</v>
+        <v>16200</v>
       </c>
       <c r="P50" s="0" t="inlineStr">
         <is>
@@ -4414,12 +4394,12 @@
       </c>
       <c r="R50" s="0" t="inlineStr">
         <is>
-          <t>S6126 Edit S6126Clone</t>
+          <t>S6347 Edit S6347Clone</t>
         </is>
       </c>
       <c r="S50" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:13 pm</t>
+          <t>09/29/2026-05:58 pm</t>
         </is>
       </c>
       <c r="T50" s="0" t="inlineStr">
@@ -4428,7 +4408,7 @@
         </is>
       </c>
       <c r="U50" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
@@ -4437,36 +4417,36 @@
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z50" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA50" s="0">
-        <v>145000</v>
+        <v>16200</v>
       </c>
       <c r="AB50" s="0">
-        <v>145000</v>
+        <v>16200</v>
       </c>
       <c r="AC50" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦145,000.00</t>
+          <t>MONIEPOINT: ₦16,200.00</t>
         </is>
       </c>
       <c r="AD50" s="0" t="inlineStr">
         <is>
-          <t>FARIDA WUDIL</t>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:31">
       <c r="A51" s="0">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>LATEST ULTRA EMBELLISHED </t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
@@ -4480,16 +4460,16 @@
         </is>
       </c>
       <c r="K51" s="0">
-        <v>38000</v>
+        <v>15000</v>
       </c>
       <c r="L51" s="0">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51" s="0">
-        <v>114000</v>
+        <v>90000</v>
       </c>
       <c r="O51" s="0">
-        <v>114000</v>
+        <v>90000</v>
       </c>
       <c r="P51" s="0" t="inlineStr">
         <is>
@@ -4503,12 +4483,12 @@
       </c>
       <c r="R51" s="0" t="inlineStr">
         <is>
-          <t>S6127 Edit S6127Clone</t>
+          <t>S6348 Edit S6348Clone</t>
         </is>
       </c>
       <c r="S51" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:15 pm</t>
+          <t>09/29/2026-05:59 pm</t>
         </is>
       </c>
       <c r="T51" s="0" t="inlineStr">
@@ -4517,7 +4497,7 @@
         </is>
       </c>
       <c r="U51" s="0">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="V51" s="0" t="inlineStr">
         <is>
@@ -4526,36 +4506,41 @@
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>HAWEE MAIDUGURI </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z51" s="0">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="AA51" s="0">
-        <v>440000</v>
+        <v>90000</v>
       </c>
       <c r="AB51" s="0">
-        <v>440000</v>
+        <v>90000</v>
       </c>
       <c r="AC51" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦440,000.00</t>
+          <t>MONIEPOINT: ₦90,000.00</t>
+        </is>
+      </c>
+      <c r="AD51" s="0" t="inlineStr">
+        <is>
+          <t>BABA HABU</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:31">
       <c r="A52" s="0">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>ABS SUPER PLAIN</t>
+          <t>LAGOS LACE C</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="G52" s="0" t="inlineStr">
@@ -4564,16 +4549,16 @@
         </is>
       </c>
       <c r="K52" s="0">
-        <v>23000</v>
+        <v>24000</v>
       </c>
       <c r="L52" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N52" s="0">
-        <v>115000</v>
+        <v>24000</v>
       </c>
       <c r="O52" s="0">
-        <v>115000</v>
+        <v>24000</v>
       </c>
       <c r="P52" s="0" t="inlineStr">
         <is>
@@ -4587,12 +4572,12 @@
       </c>
       <c r="R52" s="0" t="inlineStr">
         <is>
-          <t>S6127 Edit S6127Clone</t>
+          <t>S6349 Edit S6349Clone</t>
         </is>
       </c>
       <c r="S52" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:15 pm</t>
+          <t>09/29/2026-05:59 pm</t>
         </is>
       </c>
       <c r="T52" s="0" t="inlineStr">
@@ -4601,7 +4586,7 @@
         </is>
       </c>
       <c r="U52" s="0">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="V52" s="0" t="inlineStr">
         <is>
@@ -4610,31 +4595,36 @@
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>HAWEE MAIDUGURI </t>
+          <t>Tahir Walk-in Customers </t>
         </is>
       </c>
       <c r="Z52" s="0">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="AA52" s="0">
-        <v>440000</v>
+        <v>24000</v>
       </c>
       <c r="AB52" s="0">
-        <v>440000</v>
+        <v>24000</v>
       </c>
       <c r="AC52" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦440,000.00</t>
+          <t>MONIEPOINT: ₦24,000.00</t>
+        </is>
+      </c>
+      <c r="AD52" s="0" t="inlineStr">
+        <is>
+          <t>CTM</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:31">
       <c r="A53" s="0">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTTON POPLIN</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
@@ -4648,16 +4638,16 @@
         </is>
       </c>
       <c r="K53" s="0">
-        <v>27000</v>
+        <v>16000</v>
       </c>
       <c r="L53" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N53" s="0">
-        <v>135000</v>
+        <v>16000</v>
       </c>
       <c r="O53" s="0">
-        <v>135000</v>
+        <v>16000</v>
       </c>
       <c r="P53" s="0" t="inlineStr">
         <is>
@@ -4671,12 +4661,12 @@
       </c>
       <c r="R53" s="0" t="inlineStr">
         <is>
-          <t>S6127 Edit S6127Clone</t>
+          <t>S6350 Edit S6350Clone</t>
         </is>
       </c>
       <c r="S53" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:15 pm</t>
+          <t>09/29/2026-06:01 pm</t>
         </is>
       </c>
       <c r="T53" s="0" t="inlineStr">
@@ -4685,7 +4675,7 @@
         </is>
       </c>
       <c r="U53" s="0">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="V53" s="0" t="inlineStr">
         <is>
@@ -4694,21 +4684,21 @@
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>HAWEE MAIDUGURI </t>
+          <t>LUBABATU </t>
         </is>
       </c>
       <c r="Z53" s="0">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="AA53" s="0">
-        <v>440000</v>
+        <v>16000</v>
       </c>
       <c r="AB53" s="0">
-        <v>440000</v>
+        <v>16000</v>
       </c>
       <c r="AC53" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦440,000.00</t>
+          <t>Store Account: ₦16,000.00</t>
         </is>
       </c>
     </row>
@@ -4732,16 +4722,16 @@
         </is>
       </c>
       <c r="K54" s="0">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="L54" s="0">
         <v>3</v>
       </c>
       <c r="N54" s="0">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="O54" s="0">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="P54" s="0" t="inlineStr">
         <is>
@@ -4755,12 +4745,12 @@
       </c>
       <c r="R54" s="0" t="inlineStr">
         <is>
-          <t>S6127 Edit S6127Clone</t>
+          <t>S6351 Edit S6351Clone</t>
         </is>
       </c>
       <c r="S54" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:15 pm</t>
+          <t>09/29/2026-06:13 pm</t>
         </is>
       </c>
       <c r="T54" s="0" t="inlineStr">
@@ -4769,7 +4759,7 @@
         </is>
       </c>
       <c r="U54" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V54" s="0" t="inlineStr">
         <is>
@@ -4778,31 +4768,31 @@
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>HAWEE MAIDUGURI </t>
+          <t>Muhd Dan kasuwa Shop </t>
         </is>
       </c>
       <c r="Z54" s="0">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="AA54" s="0">
-        <v>440000</v>
+        <v>172500</v>
       </c>
       <c r="AB54" s="0">
-        <v>440000</v>
+        <v>172500</v>
       </c>
       <c r="AC54" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦440,000.00</t>
+          <t>MONIEPOINT: ₦172,500.00</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:31">
       <c r="A55" s="0">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>HOLLAND MEDIUM</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr">
@@ -4816,16 +4806,16 @@
         </is>
       </c>
       <c r="K55" s="0">
-        <v>16000</v>
+        <v>11500</v>
       </c>
       <c r="L55" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N55" s="0">
-        <v>16000</v>
+        <v>46000</v>
       </c>
       <c r="O55" s="0">
-        <v>16000</v>
+        <v>46000</v>
       </c>
       <c r="P55" s="0" t="inlineStr">
         <is>
@@ -4839,12 +4829,12 @@
       </c>
       <c r="R55" s="0" t="inlineStr">
         <is>
-          <t>S6127 Edit S6127Clone</t>
+          <t>S6351 Edit S6351Clone</t>
         </is>
       </c>
       <c r="S55" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:15 pm</t>
+          <t>09/29/2026-06:13 pm</t>
         </is>
       </c>
       <c r="T55" s="0" t="inlineStr">
@@ -4853,7 +4843,7 @@
         </is>
       </c>
       <c r="U55" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V55" s="0" t="inlineStr">
         <is>
@@ -4862,31 +4852,31 @@
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>HAWEE MAIDUGURI </t>
+          <t>Muhd Dan kasuwa Shop </t>
         </is>
       </c>
       <c r="Z55" s="0">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="AA55" s="0">
-        <v>440000</v>
+        <v>172500</v>
       </c>
       <c r="AB55" s="0">
-        <v>440000</v>
+        <v>172500</v>
       </c>
       <c r="AC55" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦440,000.00</t>
+          <t>MONIEPOINT: ₦172,500.00</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:31">
       <c r="A56" s="0">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>Win wax Holland</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
@@ -4896,20 +4886,20 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>FAHAD TAHIR (2)</t>
         </is>
       </c>
       <c r="K56" s="0">
-        <v>14500</v>
+        <v>12500</v>
       </c>
       <c r="L56" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" s="0">
-        <v>43500</v>
+        <v>25000</v>
       </c>
       <c r="O56" s="0">
-        <v>43500</v>
+        <v>25000</v>
       </c>
       <c r="P56" s="0" t="inlineStr">
         <is>
@@ -4923,12 +4913,12 @@
       </c>
       <c r="R56" s="0" t="inlineStr">
         <is>
-          <t>S6128 Edit S6128Clone</t>
+          <t>S6351 Edit S6351Clone</t>
         </is>
       </c>
       <c r="S56" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:16 pm</t>
+          <t>09/29/2026-06:13 pm</t>
         </is>
       </c>
       <c r="T56" s="0" t="inlineStr">
@@ -4937,7 +4927,7 @@
         </is>
       </c>
       <c r="U56" s="0">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V56" s="0" t="inlineStr">
         <is>
@@ -4946,31 +4936,31 @@
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>Haj Hadiza Pretty </t>
+          <t>Muhd Dan kasuwa Shop </t>
         </is>
       </c>
       <c r="Z56" s="0">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA56" s="0">
-        <v>217500</v>
+        <v>172500</v>
       </c>
       <c r="AB56" s="0">
-        <v>217500</v>
+        <v>172500</v>
       </c>
       <c r="AC56" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦217,500.00</t>
+          <t>MONIEPOINT: ₦172,500.00</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:31">
       <c r="A57" s="0">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
@@ -4980,49 +4970,49 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
+          <t> ()</t>
         </is>
       </c>
       <c r="K57" s="0">
-        <v>14500</v>
+        <v>15500</v>
       </c>
       <c r="L57" s="0">
+        <v>1</v>
+      </c>
+      <c r="N57" s="0">
+        <v>15500</v>
+      </c>
+      <c r="O57" s="0">
+        <v>15500</v>
+      </c>
+      <c r="P57" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Q57" s="0" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="R57" s="0" t="inlineStr">
+        <is>
+          <t>S6351 Edit S6351Clone</t>
+        </is>
+      </c>
+      <c r="S57" s="0" t="inlineStr">
+        <is>
+          <t>09/29/2026-06:13 pm</t>
+        </is>
+      </c>
+      <c r="T57" s="0" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="U57" s="0">
         <v>12</v>
       </c>
-      <c r="N57" s="0">
-        <v>174000</v>
-      </c>
-      <c r="O57" s="0">
-        <v>174000</v>
-      </c>
-      <c r="P57" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q57" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R57" s="0" t="inlineStr">
-        <is>
-          <t>S6128 Edit S6128Clone</t>
-        </is>
-      </c>
-      <c r="S57" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:16 pm</t>
-        </is>
-      </c>
-      <c r="T57" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U57" s="0">
-        <v>15</v>
-      </c>
       <c r="V57" s="0" t="inlineStr">
         <is>
           <t>BB </t>
@@ -5030,31 +5020,31 @@
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>Haj Hadiza Pretty </t>
+          <t>Muhd Dan kasuwa Shop </t>
         </is>
       </c>
       <c r="Z57" s="0">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA57" s="0">
-        <v>217500</v>
+        <v>172500</v>
       </c>
       <c r="AB57" s="0">
-        <v>217500</v>
+        <v>172500</v>
       </c>
       <c r="AC57" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦217,500.00</t>
+          <t>MONIEPOINT: ₦172,500.00</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:31">
       <c r="A58" s="0">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>HOLLAND MEDIUM</t>
+          <t>Super English ABC</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr">
@@ -5064,20 +5054,20 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>FAHAD TAHIR (2)</t>
         </is>
       </c>
       <c r="K58" s="0">
-        <v>12000</v>
+        <v>14500</v>
       </c>
       <c r="L58" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" s="0">
-        <v>12000</v>
+        <v>29000</v>
       </c>
       <c r="O58" s="0">
-        <v>12000</v>
+        <v>29000</v>
       </c>
       <c r="P58" s="0" t="inlineStr">
         <is>
@@ -5091,12 +5081,12 @@
       </c>
       <c r="R58" s="0" t="inlineStr">
         <is>
-          <t>S6129 Edit S6129Clone</t>
+          <t>S6351 Edit S6351Clone</t>
         </is>
       </c>
       <c r="S58" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:17 pm</t>
+          <t>09/29/2026-06:13 pm</t>
         </is>
       </c>
       <c r="T58" s="0" t="inlineStr">
@@ -5105,7 +5095,7 @@
         </is>
       </c>
       <c r="U58" s="0">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V58" s="0" t="inlineStr">
         <is>
@@ -5114,59 +5104,54 @@
       </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Muhd Dan kasuwa Shop </t>
         </is>
       </c>
       <c r="Z58" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AA58" s="0">
-        <v>92000</v>
+        <v>172500</v>
       </c>
       <c r="AB58" s="0">
-        <v>92000</v>
+        <v>172500</v>
       </c>
       <c r="AC58" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦92,000.00</t>
-        </is>
-      </c>
-      <c r="AD58" s="0" t="inlineStr">
-        <is>
-          <t>FATIMA SHARADA</t>
+          <t>MONIEPOINT: ₦172,500.00</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:31">
       <c r="A59" s="0">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>RIGHTMAN AND WISEMAN</t>
+          <t>Magic holland</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t> ()</t>
+          <t>YAYA SANI (3)</t>
         </is>
       </c>
       <c r="K59" s="0">
-        <v>5500</v>
+        <v>10300</v>
       </c>
       <c r="L59" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N59" s="0">
-        <v>55000</v>
+        <v>10300</v>
       </c>
       <c r="O59" s="0">
-        <v>55000</v>
+        <v>10300</v>
       </c>
       <c r="P59" s="0" t="inlineStr">
         <is>
@@ -5180,12 +5165,12 @@
       </c>
       <c r="R59" s="0" t="inlineStr">
         <is>
-          <t>S6129 Edit S6129Clone</t>
+          <t>S6352 Edit S6352Clone</t>
         </is>
       </c>
       <c r="S59" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:17 pm</t>
+          <t>09/29/2026-06:16 pm</t>
         </is>
       </c>
       <c r="T59" s="0" t="inlineStr">
@@ -5194,7 +5179,7 @@
         </is>
       </c>
       <c r="U59" s="0">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="V59" s="0" t="inlineStr">
         <is>
@@ -5203,41 +5188,36 @@
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Khalid Abasu Kala  </t>
         </is>
       </c>
       <c r="Z59" s="0">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="AA59" s="0">
-        <v>92000</v>
+        <v>25800</v>
       </c>
       <c r="AB59" s="0">
-        <v>92000</v>
+        <v>25800</v>
       </c>
       <c r="AC59" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦92,000.00</t>
-        </is>
-      </c>
-      <c r="AD59" s="0" t="inlineStr">
-        <is>
-          <t>FATIMA SHARADA</t>
+          <t>ACCESS BANK: ₦25,800.00</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:31">
       <c r="A60" s="0">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>TYCOON AND GAZA WOOL</t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
@@ -5246,16 +5226,16 @@
         </is>
       </c>
       <c r="K60" s="0">
-        <v>5000</v>
+        <v>15500</v>
       </c>
       <c r="L60" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N60" s="0">
-        <v>25000</v>
+        <v>15500</v>
       </c>
       <c r="O60" s="0">
-        <v>25000</v>
+        <v>15500</v>
       </c>
       <c r="P60" s="0" t="inlineStr">
         <is>
@@ -5269,12 +5249,12 @@
       </c>
       <c r="R60" s="0" t="inlineStr">
         <is>
-          <t>S6129 Edit S6129Clone</t>
+          <t>S6352 Edit S6352Clone</t>
         </is>
       </c>
       <c r="S60" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:17 pm</t>
+          <t>09/29/2026-06:16 pm</t>
         </is>
       </c>
       <c r="T60" s="0" t="inlineStr">
@@ -5283,7 +5263,7 @@
         </is>
       </c>
       <c r="U60" s="0">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="V60" s="0" t="inlineStr">
         <is>
@@ -5292,36 +5272,31 @@
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>Fahad Tahir </t>
+          <t>Khalid Abasu Kala  </t>
         </is>
       </c>
       <c r="Z60" s="0">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="AA60" s="0">
-        <v>92000</v>
+        <v>25800</v>
       </c>
       <c r="AB60" s="0">
-        <v>92000</v>
+        <v>25800</v>
       </c>
       <c r="AC60" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦92,000.00</t>
-        </is>
-      </c>
-      <c r="AD60" s="0" t="inlineStr">
-        <is>
-          <t>FATIMA SHARADA</t>
+          <t>ACCESS BANK: ₦25,800.00</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:31">
       <c r="A61" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY GOLD</t>
+          <t>CHIGANVY COTONOU PLAIN</t>
         </is>
       </c>
       <c r="E61" s="0" t="inlineStr">
@@ -5335,16 +5310,16 @@
         </is>
       </c>
       <c r="K61" s="0">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="L61" s="0">
         <v>1</v>
       </c>
       <c r="N61" s="0">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="O61" s="0">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="P61" s="0" t="inlineStr">
         <is>
@@ -5358,12 +5333,12 @@
       </c>
       <c r="R61" s="0" t="inlineStr">
         <is>
-          <t>S6130 Edit S6130Clone</t>
+          <t>S6353 Edit S6353Clone</t>
         </is>
       </c>
       <c r="S61" s="0" t="inlineStr">
         <is>
-          <t>09/23/2026-05:18 pm</t>
+          <t>09/29/2026-06:16 pm</t>
         </is>
       </c>
       <c r="T61" s="0" t="inlineStr">
@@ -5381,733 +5356,21 @@
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>HAFSAT A </t>
+          <t>MAMAN KHALIFA KATSINA</t>
         </is>
       </c>
       <c r="Z61" s="0">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="AA61" s="0">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="AB61" s="0">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="AC61" s="0" t="inlineStr">
         <is>
-          <t>Store Account: ₦25,000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" spans="1:31">
-      <c r="A62" s="0">
-        <v>219</v>
-      </c>
-      <c r="D62" s="0" t="inlineStr">
-        <is>
-          <t>Mandela kente Gold</t>
-        </is>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G62" s="0" t="inlineStr">
-        <is>
-          <t>HAFIZU TAHIR SHOP (5)</t>
-        </is>
-      </c>
-      <c r="K62" s="0">
-        <v>15000</v>
-      </c>
-      <c r="L62" s="0">
-        <v>1</v>
-      </c>
-      <c r="N62" s="0">
-        <v>15000</v>
-      </c>
-      <c r="O62" s="0">
-        <v>15000</v>
-      </c>
-      <c r="P62" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q62" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R62" s="0" t="inlineStr">
-        <is>
-          <t>S6131 Edit S6131Clone</t>
-        </is>
-      </c>
-      <c r="S62" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:18 pm</t>
-        </is>
-      </c>
-      <c r="T62" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U62" s="0">
-        <v>1</v>
-      </c>
-      <c r="V62" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W62" s="0" t="inlineStr">
-        <is>
-          <t>Fahad Tahir </t>
-        </is>
-      </c>
-      <c r="Z62" s="0">
-        <v>22</v>
-      </c>
-      <c r="AA62" s="0">
-        <v>15000</v>
-      </c>
-      <c r="AB62" s="0">
-        <v>15000</v>
-      </c>
-      <c r="AC62" s="0" t="inlineStr">
-        <is>
-          <t>Store Account: ₦15,000.00</t>
-        </is>
-      </c>
-      <c r="AD62" s="0" t="inlineStr">
-        <is>
-          <t>KULU</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" spans="1:31">
-      <c r="A63" s="0">
-        <v>196</v>
-      </c>
-      <c r="D63" s="0" t="inlineStr">
-        <is>
-          <t>Fantastic Holland</t>
-        </is>
-      </c>
-      <c r="E63" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G63" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI (3)</t>
-        </is>
-      </c>
-      <c r="K63" s="0">
-        <v>8300</v>
-      </c>
-      <c r="L63" s="0">
-        <v>4</v>
-      </c>
-      <c r="N63" s="0">
-        <v>33200</v>
-      </c>
-      <c r="O63" s="0">
-        <v>33200</v>
-      </c>
-      <c r="P63" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q63" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R63" s="0" t="inlineStr">
-        <is>
-          <t>S6132 Edit S6132Clone</t>
-        </is>
-      </c>
-      <c r="S63" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:18 pm</t>
-        </is>
-      </c>
-      <c r="T63" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U63" s="0">
-        <v>4</v>
-      </c>
-      <c r="V63" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W63" s="0" t="inlineStr">
-        <is>
-          <t>Khalid Abasu Kala  </t>
-        </is>
-      </c>
-      <c r="Z63" s="0">
-        <v>51</v>
-      </c>
-      <c r="AA63" s="0">
-        <v>33200</v>
-      </c>
-      <c r="AB63" s="0">
-        <v>33200</v>
-      </c>
-      <c r="AC63" s="0" t="inlineStr">
-        <is>
-          <t>ACCESS BANK: ₦33,200.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" spans="1:31">
-      <c r="A64" s="0">
-        <v>137</v>
-      </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t>SUPER FAMOUS</t>
-        </is>
-      </c>
-      <c r="E64" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G64" s="0" t="inlineStr">
-        <is>
-          <t> ()</t>
-        </is>
-      </c>
-      <c r="K64" s="0">
-        <v>9500</v>
-      </c>
-      <c r="L64" s="0">
-        <v>4</v>
-      </c>
-      <c r="N64" s="0">
-        <v>38000</v>
-      </c>
-      <c r="O64" s="0">
-        <v>38000</v>
-      </c>
-      <c r="P64" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q64" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R64" s="0" t="inlineStr">
-        <is>
-          <t>S6133 Edit S6133Clone</t>
-        </is>
-      </c>
-      <c r="S64" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:28 pm</t>
-        </is>
-      </c>
-      <c r="T64" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U64" s="0">
-        <v>4</v>
-      </c>
-      <c r="V64" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W64" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z64" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA64" s="0">
-        <v>38000</v>
-      </c>
-      <c r="AB64" s="0">
-        <v>38000</v>
-      </c>
-      <c r="AC64" s="0" t="inlineStr">
-        <is>
-          <t>MONIEPOINT: ₦38,000.00</t>
-        </is>
-      </c>
-      <c r="AD64" s="0" t="inlineStr">
-        <is>
-          <t>ctm</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" spans="1:31">
-      <c r="A65" s="0">
-        <v>77</v>
-      </c>
-      <c r="D65" s="0" t="inlineStr">
-        <is>
-          <t>HOLLAND WAX COLLECTION</t>
-        </is>
-      </c>
-      <c r="E65" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G65" s="0" t="inlineStr">
-        <is>
-          <t> ()</t>
-        </is>
-      </c>
-      <c r="K65" s="0">
-        <v>120000</v>
-      </c>
-      <c r="L65" s="0">
-        <v>-1</v>
-      </c>
-      <c r="N65" s="0">
-        <v>-120000</v>
-      </c>
-      <c r="O65" s="0">
-        <v>-120000</v>
-      </c>
-      <c r="P65" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q65" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R65" s="0" t="inlineStr">
-        <is>
-          <t>S6134 Edit S6134Clone</t>
-        </is>
-      </c>
-      <c r="S65" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:49 pm</t>
-        </is>
-      </c>
-      <c r="T65" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U65" s="0">
-        <v>-1</v>
-      </c>
-      <c r="V65" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W65" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z65" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA65" s="0">
-        <v>-120000</v>
-      </c>
-      <c r="AB65" s="0">
-        <v>-120000</v>
-      </c>
-      <c r="AC65" s="0" t="inlineStr">
-        <is>
-          <t>ACCESS BANK: -₦120,000.00</t>
-        </is>
-      </c>
-      <c r="AD65" s="0" t="inlineStr">
-        <is>
-          <t>ALH MOH</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" spans="1:31">
-      <c r="A66" s="0">
-        <v>104</v>
-      </c>
-      <c r="D66" s="0" t="inlineStr">
-        <is>
-          <t>CHIGANVY COTTON POPLIN</t>
-        </is>
-      </c>
-      <c r="E66" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G66" s="0" t="inlineStr">
-        <is>
-          <t> ()</t>
-        </is>
-      </c>
-      <c r="K66" s="0">
-        <v>26000</v>
-      </c>
-      <c r="L66" s="0">
-        <v>1</v>
-      </c>
-      <c r="N66" s="0">
-        <v>26000</v>
-      </c>
-      <c r="O66" s="0">
-        <v>26000</v>
-      </c>
-      <c r="P66" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q66" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R66" s="0" t="inlineStr">
-        <is>
-          <t>S6135 Edit S6135Clone</t>
-        </is>
-      </c>
-      <c r="S66" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:54 pm</t>
-        </is>
-      </c>
-      <c r="T66" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U66" s="0">
-        <v>1</v>
-      </c>
-      <c r="V66" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W66" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z66" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA66" s="0">
-        <v>26000</v>
-      </c>
-      <c r="AB66" s="0">
-        <v>26000</v>
-      </c>
-      <c r="AC66" s="0" t="inlineStr">
-        <is>
-          <t>Cash: ₦19,000.00MONIEPOINT: ₦7,000.00</t>
-        </is>
-      </c>
-      <c r="AD66" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" spans="1:31">
-      <c r="A67" s="0">
-        <v>102</v>
-      </c>
-      <c r="D67" s="0" t="inlineStr">
-        <is>
-          <t>ZAHRA BATIK</t>
-        </is>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G67" s="0" t="inlineStr">
-        <is>
-          <t> ()</t>
-        </is>
-      </c>
-      <c r="K67" s="0">
-        <v>25000</v>
-      </c>
-      <c r="L67" s="0">
-        <v>2</v>
-      </c>
-      <c r="N67" s="0">
-        <v>50000</v>
-      </c>
-      <c r="O67" s="0">
-        <v>50000</v>
-      </c>
-      <c r="P67" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q67" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R67" s="0" t="inlineStr">
-        <is>
-          <t>S6136 Edit S6136Clone</t>
-        </is>
-      </c>
-      <c r="S67" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-05:55 pm</t>
-        </is>
-      </c>
-      <c r="T67" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U67" s="0">
-        <v>2</v>
-      </c>
-      <c r="V67" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W67" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z67" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA67" s="0">
-        <v>50000</v>
-      </c>
-      <c r="AB67" s="0">
-        <v>50000</v>
-      </c>
-      <c r="AC67" s="0" t="inlineStr">
-        <is>
-          <t>MONIEPOINT: ₦50,000.00</t>
-        </is>
-      </c>
-      <c r="AD67" s="0" t="inlineStr">
-        <is>
-          <t>BABA SHUAIBU</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="1:31">
-      <c r="A68" s="0">
-        <v>142</v>
-      </c>
-      <c r="D68" s="0" t="inlineStr">
-        <is>
-          <t>HIGHOLLAND</t>
-        </is>
-      </c>
-      <c r="E68" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="G68" s="0" t="inlineStr">
-        <is>
-          <t> ()</t>
-        </is>
-      </c>
-      <c r="K68" s="0">
-        <v>4400</v>
-      </c>
-      <c r="L68" s="0">
-        <v>3</v>
-      </c>
-      <c r="N68" s="0">
-        <v>13200</v>
-      </c>
-      <c r="O68" s="0">
-        <v>13200</v>
-      </c>
-      <c r="P68" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q68" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R68" s="0" t="inlineStr">
-        <is>
-          <t>S6137 Edit S6137Clone</t>
-        </is>
-      </c>
-      <c r="S68" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-06:01 pm</t>
-        </is>
-      </c>
-      <c r="T68" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U68" s="0">
-        <v>3</v>
-      </c>
-      <c r="V68" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W68" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z68" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA68" s="0">
-        <v>13000</v>
-      </c>
-      <c r="AB68" s="0">
-        <v>13000</v>
-      </c>
-      <c r="AC68" s="0" t="inlineStr">
-        <is>
-          <t>MONIEPOINT: ₦13,000.00</t>
-        </is>
-      </c>
-      <c r="AD68" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" spans="1:31">
-      <c r="A69" s="0">
-        <v>195</v>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D69" s="0" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="E69" s="0" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="G69" s="0" t="inlineStr">
-        <is>
-          <t> ()</t>
-        </is>
-      </c>
-      <c r="K69" s="0">
-        <v>200</v>
-      </c>
-      <c r="L69" s="0">
-        <v>-1</v>
-      </c>
-      <c r="N69" s="0">
-        <v>-200</v>
-      </c>
-      <c r="O69" s="0">
-        <v>-200</v>
-      </c>
-      <c r="P69" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Q69" s="0" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="R69" s="0" t="inlineStr">
-        <is>
-          <t>S6137 Edit S6137Clone</t>
-        </is>
-      </c>
-      <c r="S69" s="0" t="inlineStr">
-        <is>
-          <t>09/23/2026-06:01 pm</t>
-        </is>
-      </c>
-      <c r="T69" s="0" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="U69" s="0">
-        <v>3</v>
-      </c>
-      <c r="V69" s="0" t="inlineStr">
-        <is>
-          <t>BB </t>
-        </is>
-      </c>
-      <c r="W69" s="0" t="inlineStr">
-        <is>
-          <t>Tahir Walk-in Customers </t>
-        </is>
-      </c>
-      <c r="Z69" s="0">
-        <v>23</v>
-      </c>
-      <c r="AA69" s="0">
-        <v>13000</v>
-      </c>
-      <c r="AB69" s="0">
-        <v>13000</v>
-      </c>
-      <c r="AC69" s="0" t="inlineStr">
-        <is>
-          <t>MONIEPOINT: ₦13,000.00</t>
-        </is>
-      </c>
-      <c r="AD69" s="0" t="inlineStr">
-        <is>
-          <t>CTM</t>
+          <t>Store Account: ₦20,000.00</t>
         </is>
       </c>
     </row>
